--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V152"/>
+  <dimension ref="A1:V155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>[{'arquivo': 'AES 85548 4600026463 HAGAP.pdf', 'ae': '084548'}]</t>
+          <t>[{'arquivo': 'AES 85548 4600026463 HAGAP.pdf', 'ae': '084548'}, {'arquivo': 'AES 84548 4600026463 HAGAP.pdf', 'ae': '084548'}]</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
-          <t>[{'arquivo': 'AES 85548 4600026463 HAGAP.pdf', 'ae': '084548'}]</t>
+          <t>[{'arquivo': 'AES 85548 4600026463 HAGAP.pdf', 'ae': '084548'}, {'arquivo': 'AES 84548 4600026463 HAGAP.pdf', 'ae': '084548'}]</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
-          <t>[{'arquivo': 'AES 85548 4600026463 HAGAP.pdf', 'ae': '084548'}]</t>
+          <t>[{'arquivo': 'AES 85548 4600026463 HAGAP.pdf', 'ae': '084548'}, {'arquivo': 'AES 84548 4600026463 HAGAP.pdf', 'ae': '084548'}]</t>
         </is>
       </c>
     </row>
@@ -7018,15 +7018,23 @@
           <t>1714348</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>084552</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>DESAOJORGEDOPATROCINIO RURAL</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>90,022</t>
+        </is>
+      </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>90.02200000000001</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7038,7 +7046,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>R$6.874,07</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -7059,7 +7071,11 @@
       <c r="P84" t="n">
         <v>5</v>
       </c>
-      <c r="Q84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>AES 84552 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr">
         <is>
           <t>1714348 01.20263383601119 - MUNICIPIO DE SAO JORGE DO PATROCINIO 29.06</t>
@@ -7067,12 +7083,16 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84552 4600026463 HAGAP.pdf', 'ae': '084552'}]</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10662,6 +10682,192 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1727778I</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>084624</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>47,524</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>47.524</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>R$3.628,93</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J153" t="b">
+        <v>0</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>AES 84624 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84624 4600026463 HAGAP.pdf', 'ae': '084624'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1727778</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TUNEIRASDOOESTE</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J154" t="b">
+        <v>0</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>1727778 - Melhoria URGENTE</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1677316</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J155" t="b">
+        <v>0</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V155"/>
+  <dimension ref="A1:V165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -825,11 +825,15 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -849,7 +853,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4201,11 +4205,15 @@
       <c r="J47" t="b">
         <v>0</v>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -4225,7 +4233,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -9421,24 +9429,32 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -9521,24 +9537,32 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -9721,24 +9745,32 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P134" t="n">
         <v>0</v>
@@ -9771,24 +9803,32 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P135" t="n">
         <v>0</v>
@@ -10245,24 +10285,32 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -10295,24 +10343,32 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
@@ -10345,24 +10401,32 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
@@ -10395,24 +10459,32 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P147" t="n">
         <v>0</v>
@@ -10506,10 +10578,14 @@
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -10545,24 +10621,32 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
       <c r="N150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
@@ -10595,24 +10679,32 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
@@ -10868,6 +10960,518 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1658452</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J156" t="b">
+        <v>1</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="n">
+        <v>1</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1510407</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J157" t="b">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1713240</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J158" t="b">
+        <v>1</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>20.05.2026</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1713933</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J159" t="b">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1671139I</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J160" t="b">
+        <v>1</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="n">
+        <v>1</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1715920</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J161" t="b">
+        <v>0</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1694258</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J162" t="b">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1710735</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J163" t="b">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1712530</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J164" t="b">
+        <v>0</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J165" t="b">
+        <v>0</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V165"/>
+  <dimension ref="A1:V170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,11 +657,15 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -681,7 +685,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -11472,6 +11476,336 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1727808I</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>084796</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>121,685</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>121.685</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>R$8.676,98</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J166" t="b">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>AES 84796 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>⚠ AE '084796' em múltiplos projetos: 1727808I, 1728163I</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84796 4600026463 HAGAP.pdf', 'ae': '084796'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1728163I</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>084796</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>121,685</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>121.685</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>R$8.676,98</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J167" t="b">
+        <v>0</v>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>AES 84796 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>⚠ AE '084796' em múltiplos projetos: 1727808I, 1728163I</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84796 4600026463 HAGAP.pdf', 'ae': '084796'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J168" t="b">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>1727808 UC 17399556 _CTO 8940815214_SS 20264161400821</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1728163</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J169" t="b">
+        <v>0</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>1728163 UC 106615580_CTO 8940847951_SS 20264367568796</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1676605</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J170" t="b">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V170"/>
+  <dimension ref="A1:V191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,7 +727,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3967,11 +3967,19 @@
       <c r="J44" t="b">
         <v>0</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -3991,7 +3999,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -4717,7 +4725,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4803,7 +4811,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4889,7 +4897,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4971,7 +4979,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5049,7 +5057,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5213,7 +5221,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5299,7 +5307,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5381,7 +5389,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -11454,10 +11462,14 @@
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -11784,10 +11796,14 @@
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -11805,6 +11821,1652 @@
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1721887</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>084868</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>818,659</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>818.659</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>R$60.918,10</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J171" t="b">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>AES 84868 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>1721887 01.20263889730899 - EPR PARANA S.A 17.07 PARALISADO NÃO EXECUTAR</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>⚠ AE '084868' em múltiplos projetos: 1721887, 1725071, 1722321, 1724356, 1724172, 1724680</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84868 4600026463 HAGAP.pdf', 'ae': '084868'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1725071</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>084868</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>818,659</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>818.659</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>R$60.918,10</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J172" t="b">
+        <v>0</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>AES 84868 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>1725071 01.20263889932791 - EPR PARANA S.A 17.07</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>⚠ AE '084868' em múltiplos projetos: 1721887, 1725071, 1722321, 1724356, 1724172, 1724680</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84868 4600026463 HAGAP.pdf', 'ae': '084868'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1722321</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>084868</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>818,659</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>818.659</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>R$60.918,10</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J173" t="b">
+        <v>0</v>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>AES 84868 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>1722321 01.20263963899660 - PEDRO GABRIEL PEREIRA MANTOVANI 20.07</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>⚠ AE '084868' em múltiplos projetos: 1721887, 1725071, 1722321, 1724356, 1724172, 1724680</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84868 4600026463 HAGAP.pdf', 'ae': '084868'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>084868</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>818,659</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>818.659</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>R$60.918,10</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J174" t="b">
+        <v>0</v>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>AES 84868 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>1724356 01.20264076711397 - JAIME FIGUEIREDO DE QUEIROZ 13.07</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>⚠ AE '084868' em múltiplos projetos: 1721887, 1725071, 1722321, 1724356, 1724172, 1724680</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84868 4600026463 HAGAP.pdf', 'ae': '084868'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1724172</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>084868</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ANUNCIACAO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>818,659</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>818.659</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>R$60.918,10</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J175" t="b">
+        <v>0</v>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>AES 84868 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>1724172 01.20264057824417 - MERCEDES MARTINS BENOSSE 20.07</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>⚠ AE '084868' em múltiplos projetos: 1721887, 1725071, 1722321, 1724356, 1724172, 1724680</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84868 4600026463 HAGAP.pdf', 'ae': '084868'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1724680</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>084868</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>818,659</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>818.659</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>R$60.918,10</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J176" t="b">
+        <v>0</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>AES 84868 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>1724680 01.20264127888234 - WELINGTON SCHIAVO 20.07</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>⚠ AE '084868' em múltiplos projetos: 1721887, 1725071, 1722321, 1724356, 1724172, 1724680</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84868 4600026463 HAGAP.pdf', 'ae': '084868'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1698056I</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>084872</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>725,998</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>725.998</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>R$52.950,36</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J177" t="b">
+        <v>0</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>AES 84872 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>⚠ AE '084872' em múltiplos projetos: 1698056I, 1722803, 1725370, 1726062</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84872 4600026463 HAGAP.pdf', 'ae': '084872'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1722803</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>084872</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>725,998</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>725.998</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>R$52.950,36</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J178" t="b">
+        <v>0</v>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>AES 84872 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>1722803 01.20263889198020 - EPR PARANA S.A 14.09</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>⚠ AE '084872' em múltiplos projetos: 1698056I, 1722803, 1725370, 1726062</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84872 4600026463 HAGAP.pdf', 'ae': '084872'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1725370</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>084872</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>725,998</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>725.998</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>R$52.950,36</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J179" t="b">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>AES 84872 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>1725370 01.20264129549248 - RODRIGO ANDERSON GRECCO 01.11</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>⚠ AE '084872' em múltiplos projetos: 1698056I, 1722803, 1725370, 1726062</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84872 4600026463 HAGAP.pdf', 'ae': '084872'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1726062</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>084872</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>725,998</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>725.998</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>R$52.950,36</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J180" t="b">
+        <v>0</v>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>AES 84872 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>1726062 01.20264109805762 - CAMILA AGOSTINIS FREIRE BARRANCO - FALTA PROJETO EDUARDO 14.09</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>⚠ AE '084872' em múltiplos projetos: 1698056I, 1722803, 1725370, 1726062</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84872 4600026463 HAGAP.pdf', 'ae': '084872'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1714342</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>084904</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>331,320</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>R$22.187,97</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J181" t="b">
+        <v>0</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>AES 84904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>1714342 01.20263383520658 - HOMILTO GONCALVES DA SILVA 20.07</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>⚠ AE '084904' em múltiplos projetos: 1714342, 1715146, 1719159, 1721175, 1724663, 1727187I</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84904 4600026463 HAGAP.pdf', 'ae': '084904'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1715146</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>084904</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SILVA AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>331,320</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>R$22.187,97</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J182" t="b">
+        <v>0</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>AES 84904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>1715146 01.20263406066524 - DONIZETE SCARANTE 20.07</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>⚠ AE '084904' em múltiplos projetos: 1714342, 1715146, 1719159, 1721175, 1724663, 1727187I</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84904 4600026463 HAGAP.pdf', 'ae': '084904'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1719159</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>084904</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>331,320</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>R$22.187,97</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J183" t="b">
+        <v>0</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>AES 84904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>1719159 01.20263673771749 - ADRIANO VALERIO FRANCO 20.07</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>⚠ AE '084904' em múltiplos projetos: 1714342, 1715146, 1719159, 1721175, 1724663, 1727187I</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84904 4600026463 HAGAP.pdf', 'ae': '084904'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1721175</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>084904</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>331,320</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>R$22.187,97</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J184" t="b">
+        <v>0</v>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>AES 84904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>1721175 01.20263847556908 - DANIEL ANTONIO MARTINS 22.05</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>⚠ AE '084904' em múltiplos projetos: 1714342, 1715146, 1719159, 1721175, 1724663, 1727187I</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84904 4600026463 HAGAP.pdf', 'ae': '084904'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1724663</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>084904</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SILVA AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>331,320</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>R$22.187,97</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J185" t="b">
+        <v>0</v>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>AES 84904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>1724663 01.20264056811595 - ASILO SAO VICENTE DE PAULO DE TERRA BOA 24.07</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>⚠ AE '084904' em múltiplos projetos: 1714342, 1715146, 1719159, 1721175, 1724663, 1727187I</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84904 4600026463 HAGAP.pdf', 'ae': '084904'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1727187I</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>084904</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>331,320</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>R$22.187,97</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J186" t="b">
+        <v>0</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>AES 84904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>⚠ AE '084904' em múltiplos projetos: 1714342, 1715146, 1719159, 1721175, 1724663, 1727187I</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 84904 4600026463 HAGAP.pdf', 'ae': '084904'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1698056</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>DECIANORTE</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>R$7.099,38</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J187" t="b">
+        <v>0</v>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>1698056 01.20263726787324 - MUNICIPIO DE CIANORTE 18.05</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1727187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CRUZEIRODOOESTE</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J188" t="b">
+        <v>0</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>1727187 UC 18990053 - CTO 8940821152 - SS 20264303761888</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1663556I</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J189" t="b">
+        <v>1</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" t="n">
+        <v>1</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1704968</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J190" t="b">
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>29.05.2026</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" t="n">
+        <v>1</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1704525</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J191" t="b">
+        <v>0</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V191"/>
+  <dimension ref="A1:V216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2435,24 +2435,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2507,7 +2515,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3389,7 +3397,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3475,7 +3483,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3553,7 +3561,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3631,7 +3639,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5471,7 +5479,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5557,7 +5565,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -10247,24 +10255,32 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -11451,11 +11467,11 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -11467,12 +11483,16 @@
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
       <c r="N165" t="n">
         <v>2</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -13468,6 +13488,1532 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1706327</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ARAPUA</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>80,635</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>80.63500000000001</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J192" t="b">
+        <v>0</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>1706327</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1706336</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>E M</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>140,125</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>140.125</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J193" t="b">
+        <v>0</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>1706336</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1711120</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>NOVA TEBAS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>103,840</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>103.84</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J194" t="b">
+        <v>0</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>1711120</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1711629</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>02.03.2027</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J195" t="b">
+        <v>0</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>1711629 01.20263195647434 - ALESSANDRO SAMPAIO RIBEIRO 20.07</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1711788</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ESPERANÇA NOVA</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J196" t="b">
+        <v>0</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>1711788 01.20263240861110 - ASSOCIACAO COMUNITARIA TERRA BOA 20.07</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1713681</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>02.03.2027</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J197" t="b">
+        <v>0</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>1713681 01.20263343447907 - JHIMY KENEDY SOUZA FERRARI 20.07</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1716557</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>CIANORTE</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>825,664</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>825.664</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J198" t="b">
+        <v>0</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>1716557 - LDNU335802024   - croqui 3. Cianorte</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1716612</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CIANORTE</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>32,420</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J199" t="b">
+        <v>0</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>1716612  -LDNU335802024 - croqui 3. Cianorte</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1718441</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>WESLEY ORTIZ DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>942,003</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>942.003</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J200" t="b">
+        <v>0</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>1718441 -LDNU335802024 - croqui 3. Cianorte</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1719077</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J201" t="b">
+        <v>0</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>1719077 01.20263579349056 - SALVADOR ZANOLI 18.09</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1721898</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SILVA AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J202" t="b">
+        <v>0</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>1721898 01.20263889505744 - EPR PARANA S.A 16.09</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1724051</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>11.05.2027</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>R$2.765,41</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J203" t="b">
+        <v>0</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>1724051 01.20264075681748 - MARIO SERGIO DE OLIVEIRA 17.11</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1724053</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>30.12.2027</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J204" t="b">
+        <v>0</v>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>1724053 01.20263997605660 - JESSICA FERNANDA BONIFACIO DOS SANTOS 24.07</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1724174</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>13.05.2027</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>R$0.000,00</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J205" t="b">
+        <v>0</v>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>1724174 01.20264077495618 - SECRETARIA DE ESTADO DA EDUCACAO SEED 21.09</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J206" t="b">
+        <v>0</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>1724491 01.20264110172007 - GILMAR ALEIXO 23.09</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1724537</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>02.05.2027</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J207" t="b">
+        <v>0</v>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>1724537 01.20263968582955 - AGUINEL FERREIRA DA CRUZ 03.08</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1724550</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>15.05.2027</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J208" t="b">
+        <v>0</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>1724550 01.20264098016709 - ASSOCIACAO DO NUCLEO DE PRODUCAO DOS IDOSOS DE ALTONIA PR 3 IDADE 18.09</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1724558</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SILVA AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>01.09.2027</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J209" t="b">
+        <v>0</v>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>1724558 01.20263889412776 - EPR PARANA S.A 19.05.2027</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ANUNCIACAO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>19.05.2027</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>R$ 30.884,03</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J210" t="b">
+        <v>0</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>1725260 01.20264163756882 - CONSTRUTORA RVA LTDA 27.07</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1725686</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>18.05.2027</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J211" t="b">
+        <v>0</v>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>1725686 01.20264132155190 - JOAO DA SILVA NETO 23.09</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1726318</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>21.12.2026</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J212" t="b">
+        <v>0</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>1726318 01.20264173095321 - VIVIANE FERREIRA CAMILO GONZAGA 22.09</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1726324</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>23.11.2026</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J213" t="b">
+        <v>0</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>1726324 01.20264187424019 - SILVIO YNAMURA 31.07</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1726942</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>R$2.624,69</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J214" t="b">
+        <v>0</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>1726942 01.20264264580530 - AFONSO DE OLIVEIRA BERTONCELO 17.11</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1728642</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>GIOVANNI M CARVALHO</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J215" t="b">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>1728642 01.20264308973713 - EVANDO APARECIDO BORGES SILVA 30.07</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1712766I</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J216" t="b">
+        <v>0</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>08.06.2026</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="n">
+        <v>2</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V216"/>
+  <dimension ref="A1:V222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,7 +981,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6831,11 +6831,15 @@
       <c r="J80" t="b">
         <v>0</v>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -6851,7 +6855,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -11873,7 +11877,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11959,7 +11963,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12045,7 +12049,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12131,7 +12135,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12217,7 +12221,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -12303,7 +12307,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -15014,6 +15018,314 @@
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1718803</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J217" t="b">
+        <v>1</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>1</v>
+      </c>
+      <c r="O217" t="n">
+        <v>1</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1648254</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J218" t="b">
+        <v>1</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>1</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1667593</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J219" t="b">
+        <v>1</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1</v>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J220" t="b">
+        <v>0</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1704867</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J221" t="b">
+        <v>1</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>19.05.2026</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="n">
+        <v>1</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1692636</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J222" t="b">
+        <v>0</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="n">
+        <v>1</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V222"/>
+  <dimension ref="A1:V238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9253,24 +9253,32 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" t="n">
         <v>0</v>
@@ -9303,24 +9311,32 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -9403,24 +9419,32 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>12.06.2026</t>
+        </is>
+      </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -15326,6 +15350,998 @@
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1704074</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>JAPURA</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>23.03.2027</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>R$70.485,69</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J223" t="b">
+        <v>0</v>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>1704074 01.20252342373790 - SERVICO AUTONOMO MUNICIPAL DE AGUA E ESGOTO</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1706325</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>C L F</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>140,360</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>140.36</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J224" t="b">
+        <v>0</v>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>1706325 Finalização TK</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1722805</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>02.04.2027</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>R$53.481,65</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J225" t="b">
+        <v>0</v>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>1722805 01.20263889838038 - EPR PARANA S.A 16.09</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1722845</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SILVA AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>01.09.2027</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J226" t="b">
+        <v>0</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>1722845 01.20263890080326 - EPR PARANA S.A 19.05.2027</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1723691</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>08.05.2027</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J227" t="b">
+        <v>0</v>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>1723691 01.20264027799054 - ASSOCIACAO ASSISTENCIAL E PROMOCIONAL CASA DA PAZ 16.09</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1726007</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J228" t="b">
+        <v>0</v>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>1726007 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1726008</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>FAZER JUMPER</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J229" t="b">
+        <v>0</v>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>1726008 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1726018</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J230" t="b">
+        <v>0</v>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>1726018 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1726033</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>H H</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J231" t="b">
+        <v>0</v>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>1726033 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J232" t="b">
+        <v>0</v>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>1726042 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1726044</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J233" t="b">
+        <v>0</v>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>1726044 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1726045</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TNO</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J234" t="b">
+        <v>0</v>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>1726045 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1726058</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J235" t="b">
+        <v>0</v>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>1726058 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1727881</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>PREFEITURA DE CIANORTE</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>R$2.757,73</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J236" t="b">
+        <v>0</v>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>1727881 20264266857004 - MUNICIPIO DE CIANORTE 30.07</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1729112</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J237" t="b">
+        <v>0</v>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>1729112 - Melhoria Tensão</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr"/>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1729397</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J238" t="b">
+        <v>0</v>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>1729397 UC 69928010_CTO 8940800172_ SS 20264438037135</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V238"/>
+  <dimension ref="A1:V253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2897,7 +2897,11 @@
           <t>083980</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>1.080,951</t>
@@ -2943,17 +2947,21 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>AES 83980 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1715688 01.20263463790410 - IRINEU ROMERO FERRARINI</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>ae, medicao</t>
+          <t>ae, medicao, pasta</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -4209,7 +4217,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4299,7 +4307,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4385,7 +4393,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4471,7 +4479,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4561,7 +4569,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4647,7 +4655,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4931,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -5003,11 +5011,15 @@
       <c r="J56" t="b">
         <v>0</v>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -5023,7 +5035,7 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -5081,11 +5093,15 @@
       <c r="J57" t="b">
         <v>0</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -5101,7 +5117,7 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -9643,24 +9659,32 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
       <c r="N131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -9693,24 +9717,32 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>15.06.2026</t>
+        </is>
+      </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
@@ -9743,24 +9775,32 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -10573,24 +10613,32 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P148" t="n">
         <v>0</v>
@@ -12753,7 +12801,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12839,7 +12887,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12925,7 +12973,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13011,7 +13059,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13097,7 +13145,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13179,7 +13227,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -16342,6 +16390,904 @@
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1667141</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J239" t="b">
+        <v>1</v>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>2</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
+      <c r="V239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1726057</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>WESLEY ORTIZ DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J240" t="b">
+        <v>0</v>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>1726057 ALNU392492026</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr"/>
+      <c r="U240" t="inlineStr"/>
+      <c r="V240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1726332</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>DETAPIRA CENTRO</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J241" t="b">
+        <v>0</v>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>1726332 01.20264236490327 - MUNICIPIO DE TAPIRA 03.08</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr"/>
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1726388</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>28.05.2027</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J242" t="b">
+        <v>0</v>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>1726388 01.20264187294588 - APARECIDA DE FATIMA PASCHOAL ANTONIEL 29.09</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr"/>
+      <c r="U242" t="inlineStr"/>
+      <c r="V242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1726541</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>DEUMUARAMA DISTRDELOVAT</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>31.05.2027</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>R$42,95</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J243" t="b">
+        <v>0</v>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>1726541 01.20264247833541 - MUNICIPIO DE UMUARAMA</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr"/>
+      <c r="U243" t="inlineStr"/>
+      <c r="V243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>DETERRABOA JDSENA</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>29.05.2027</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>R$ 11.143,51</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J244" t="b">
+        <v>0</v>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>1726890 01.20264225253150 - MUNICIPIO DE TERRA BOA 03.08</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1727335</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>DEMOREIRASALES MORADADOSOLJD</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>02.12.2026</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>R$ 8.079,08</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J245" t="b">
+        <v>0</v>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>1727335 01.20264269641920 - MUNICIPIO DE MOREIRA SALES 10.08</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ESTRADA FUMAÇA - XAMBRE</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J246" t="b">
+        <v>0</v>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>1730222 01.20263660657526 - MARCELO MENDES DE OLIVEIRA 05.08</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1730642</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J247" t="b">
+        <v>0</v>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>1730642 UC 73279862_CTO 8940809878_ SS 20264531082338</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr"/>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1730761</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>MAICON LUIZ WATHIER</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>30.06.2027</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J248" t="b">
+        <v>0</v>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>1730761 -SE em CIANORTE</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr"/>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1730908</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>CIANORTE</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>30.06.2027</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J249" t="b">
+        <v>0</v>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>1730908 - SE em CIANORTE</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr"/>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1683861I</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J250" t="b">
+        <v>0</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr"/>
+      <c r="U250" t="inlineStr"/>
+      <c r="V250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1715278</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J251" t="b">
+        <v>0</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="n">
+        <v>1</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr"/>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1675389I</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J252" t="b">
+        <v>1</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="n">
+        <v>1</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr"/>
+      <c r="U252" t="inlineStr"/>
+      <c r="V252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1715257I</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J253" t="b">
+        <v>1</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>16.06.2026</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>1</v>
+      </c>
+      <c r="O253" t="n">
+        <v>1</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr"/>
+      <c r="U253" t="inlineStr"/>
+      <c r="V253" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V253"/>
+  <dimension ref="A1:V278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,11 +1247,15 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1271,7 +1275,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2531,11 +2535,15 @@
       <c r="J26" t="b">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2551,7 +2559,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2691,11 +2699,15 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2711,7 +2723,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -2851,11 +2863,15 @@
       <c r="J30" t="b">
         <v>0</v>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -2871,7 +2887,7 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3175,11 +3191,15 @@
       <c r="J34" t="b">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3195,7 +3215,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3507,11 +3527,15 @@
       <c r="J38" t="b">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3527,7 +3551,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -3579,20 +3603,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3605,7 +3637,7 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3663,11 +3695,15 @@
       <c r="J40" t="b">
         <v>0</v>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -3683,7 +3719,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -4323,11 +4359,15 @@
       <c r="J48" t="b">
         <v>0</v>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -4347,7 +4387,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -4409,11 +4449,15 @@
       <c r="J49" t="b">
         <v>0</v>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -4433,7 +4477,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4585,11 +4629,15 @@
       <c r="J51" t="b">
         <v>0</v>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -4609,7 +4657,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4757,11 +4805,15 @@
       <c r="J53" t="b">
         <v>0</v>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -4781,7 +4833,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -4929,11 +4981,15 @@
       <c r="J55" t="b">
         <v>0</v>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -4953,7 +5009,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6113,11 +6169,15 @@
       <c r="J69" t="b">
         <v>0</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -6137,7 +6197,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -6277,11 +6337,15 @@
       <c r="J71" t="b">
         <v>0</v>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -6301,7 +6365,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -6363,11 +6427,15 @@
       <c r="J72" t="b">
         <v>0</v>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -6387,7 +6455,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -6449,11 +6517,15 @@
       <c r="J73" t="b">
         <v>0</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -6473,7 +6545,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -10905,7 +10977,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11705,11 +11777,15 @@
       <c r="J167" t="b">
         <v>0</v>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -11725,7 +11801,7 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
@@ -11965,11 +12041,15 @@
       <c r="J171" t="b">
         <v>0</v>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -11989,7 +12069,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -12223,11 +12303,15 @@
       <c r="J174" t="b">
         <v>0</v>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -12247,7 +12331,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -12477,11 +12561,15 @@
       <c r="J177" t="b">
         <v>0</v>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -12497,7 +12585,7 @@
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -12817,11 +12905,15 @@
       <c r="J181" t="b">
         <v>0</v>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -12841,7 +12933,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -14451,11 +14543,15 @@
       <c r="J206" t="b">
         <v>0</v>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -14471,7 +14567,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -14703,11 +14799,15 @@
       <c r="J210" t="b">
         <v>0</v>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -14723,7 +14823,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -15718,15 +15818,23 @@
           <t>1726007</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>085280</t>
+        </is>
+      </c>
       <c r="C228" t="inlineStr">
         <is>
           <t>TUNEIRAS DO OESTE</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1.842,380</t>
+        </is>
+      </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>1842.38</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -15738,7 +15846,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>R$140.684,13</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15759,7 +15871,11 @@
       <c r="P228" t="n">
         <v>6</v>
       </c>
-      <c r="Q228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>AES 85280 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R228" t="inlineStr">
         <is>
           <t>1726007 ALNU392492026</t>
@@ -15767,12 +15883,16 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
       <c r="U228" t="inlineStr"/>
-      <c r="V228" t="inlineStr"/>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85280 4600026463 HAGAP.pdf', 'ae': '085280'}]</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15780,15 +15900,23 @@
           <t>1726008</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>085281</t>
+        </is>
+      </c>
       <c r="C229" t="inlineStr">
         <is>
           <t>FAZER JUMPER</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2.660,997</t>
+        </is>
+      </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>2660.997</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -15800,7 +15928,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>R$203.193,73</t>
+        </is>
+      </c>
       <c r="I229" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15821,7 +15953,11 @@
       <c r="P229" t="n">
         <v>5</v>
       </c>
-      <c r="Q229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>AES 85281 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R229" t="inlineStr">
         <is>
           <t>1726008 ALNU392492026</t>
@@ -15829,12 +15965,16 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr"/>
-      <c r="V229" t="inlineStr"/>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85281 4600026463 HAGAP.pdf', 'ae': '085281'}]</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15842,15 +15982,23 @@
           <t>1726018</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>085282</t>
+        </is>
+      </c>
       <c r="C230" t="inlineStr">
         <is>
           <t>TUNEIRAS DO OESTE</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2.479,127</t>
+        </is>
+      </c>
       <c r="E230" t="n">
-        <v>0</v>
+        <v>2479.127</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -15862,7 +16010,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>R$189.306,13</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15883,7 +16035,11 @@
       <c r="P230" t="n">
         <v>2</v>
       </c>
-      <c r="Q230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>AES 85282 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R230" t="inlineStr">
         <is>
           <t>1726018 ALNU392492026</t>
@@ -15891,12 +16047,16 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
       <c r="U230" t="inlineStr"/>
-      <c r="V230" t="inlineStr"/>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85282 4600026463 HAGAP.pdf', 'ae': '085282'}]</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15904,15 +16064,23 @@
           <t>1726033</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>085283</t>
+        </is>
+      </c>
       <c r="C231" t="inlineStr">
         <is>
           <t>H H</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2.213,437</t>
+        </is>
+      </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>2213.437</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -15924,7 +16092,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>R$169.018,04</t>
+        </is>
+      </c>
       <c r="I231" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15945,7 +16117,11 @@
       <c r="P231" t="n">
         <v>6</v>
       </c>
-      <c r="Q231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>AES 85283 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R231" t="inlineStr">
         <is>
           <t>1726033 ALNU392492026</t>
@@ -15953,12 +16129,16 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
-      <c r="V231" t="inlineStr"/>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85283 4600026463 HAGAP.pdf', 'ae': '085283'}]</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15966,15 +16146,23 @@
           <t>1726042</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>085284</t>
+        </is>
+      </c>
       <c r="C232" t="inlineStr">
         <is>
           <t>TUNEIRAS DO OESTE</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2.521,586</t>
+        </is>
+      </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>2521.586</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -15986,7 +16174,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>R$192.548,30</t>
+        </is>
+      </c>
       <c r="I232" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16007,7 +16199,11 @@
       <c r="P232" t="n">
         <v>5</v>
       </c>
-      <c r="Q232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>AES 85284 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R232" t="inlineStr">
         <is>
           <t>1726042 ALNU392492026</t>
@@ -16015,12 +16211,16 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr"/>
-      <c r="V232" t="inlineStr"/>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85284 4600026463 HAGAP.pdf', 'ae': '085284'}]</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16028,15 +16228,23 @@
           <t>1726044</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>085286</t>
+        </is>
+      </c>
       <c r="C233" t="inlineStr">
         <is>
           <t>TUNEIRAS DO OESTE</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2.190,844</t>
+        </is>
+      </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>2190.844</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -16048,7 +16256,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>R$167.292,84</t>
+        </is>
+      </c>
       <c r="I233" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16069,7 +16281,11 @@
       <c r="P233" t="n">
         <v>6</v>
       </c>
-      <c r="Q233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>AES 85286 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R233" t="inlineStr">
         <is>
           <t>1726044 ALNU392492026</t>
@@ -16077,12 +16293,16 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
-      <c r="V233" t="inlineStr"/>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85286 4600026463 HAGAP.pdf', 'ae': '085286'}]</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16090,15 +16310,23 @@
           <t>1726045</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>085287</t>
+        </is>
+      </c>
       <c r="C234" t="inlineStr">
         <is>
           <t>TNO</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>1.663,132</t>
+        </is>
+      </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>1663.132</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -16110,7 +16338,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>R$126.996,75</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16131,7 +16363,11 @@
       <c r="P234" t="n">
         <v>4</v>
       </c>
-      <c r="Q234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>AES 85287 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R234" t="inlineStr">
         <is>
           <t>1726045 ALNU392492026</t>
@@ -16139,12 +16375,16 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr"/>
-      <c r="V234" t="inlineStr"/>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85287 4600026463 HAGAP.pdf', 'ae': '085287'}]</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16152,15 +16392,23 @@
           <t>1726058</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>085289</t>
+        </is>
+      </c>
       <c r="C235" t="inlineStr">
         <is>
           <t>TUNEIRAS DO OESTE</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>1.746,390</t>
+        </is>
+      </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>1746.39</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -16172,7 +16420,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>R$133.354,34</t>
+        </is>
+      </c>
       <c r="I235" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16193,7 +16445,11 @@
       <c r="P235" t="n">
         <v>2</v>
       </c>
-      <c r="Q235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>AES 85289 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R235" t="inlineStr">
         <is>
           <t>1726058 ALNU392492026</t>
@@ -16201,12 +16457,16 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr"/>
-      <c r="V235" t="inlineStr"/>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85289 4600026463 HAGAP.pdf', 'ae': '085289'}]</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16454,15 +16714,23 @@
           <t>1726057</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>085305</t>
+        </is>
+      </c>
       <c r="C240" t="inlineStr">
         <is>
           <t>WESLEY ORTIZ DE OLIVEIRA</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.573,452</t>
+        </is>
+      </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>2573.452</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -16474,7 +16742,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>R$196.508,79</t>
+        </is>
+      </c>
       <c r="I240" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16495,7 +16767,11 @@
       <c r="P240" t="n">
         <v>10</v>
       </c>
-      <c r="Q240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>AES 85305 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R240" t="inlineStr">
         <is>
           <t>1726057 ALNU392492026</t>
@@ -16503,12 +16779,16 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr"/>
-      <c r="V240" t="inlineStr"/>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85305 4600026463 HAGAP.pdf', 'ae': '085305'}]</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16516,15 +16796,23 @@
           <t>1726332</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>085301</t>
+        </is>
+      </c>
       <c r="C241" t="inlineStr">
         <is>
           <t>DETAPIRA CENTRO</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>406,703</t>
+        </is>
+      </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>406.703</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -16536,7 +16824,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>R$28.896,74</t>
+        </is>
+      </c>
       <c r="I241" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16557,7 +16849,11 @@
       <c r="P241" t="n">
         <v>4</v>
       </c>
-      <c r="Q241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>AES 85301 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R241" t="inlineStr">
         <is>
           <t>1726332 01.20264236490327 - MUNICIPIO DE TAPIRA 03.08</t>
@@ -16565,12 +16861,20 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T241" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>⚠ AE '085301' em múltiplos projetos: 1726332, 1726890, 1730222</t>
+        </is>
+      </c>
       <c r="U241" t="inlineStr"/>
-      <c r="V241" t="inlineStr"/>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85301 4600026463 HAGAP.pdf', 'ae': '085301'}]</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -16578,15 +16882,23 @@
           <t>1726388</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>085302</t>
+        </is>
+      </c>
       <c r="C242" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>621,892</t>
+        </is>
+      </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>621.8920000000001</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -16598,7 +16910,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>R$41.833,50</t>
+        </is>
+      </c>
       <c r="I242" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16619,7 +16935,11 @@
       <c r="P242" t="n">
         <v>3</v>
       </c>
-      <c r="Q242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>AES 85302 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R242" t="inlineStr">
         <is>
           <t>1726388 01.20264187294588 - APARECIDA DE FATIMA PASCHOAL ANTONIEL 29.09</t>
@@ -16627,12 +16947,20 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T242" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>⚠ AE '085302' em múltiplos projetos: 1726388, 1726541</t>
+        </is>
+      </c>
       <c r="U242" t="inlineStr"/>
-      <c r="V242" t="inlineStr"/>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85302 4600026463 HAGAP.pdf', 'ae': '085302'}]</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -16640,15 +16968,23 @@
           <t>1726541</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>085302</t>
+        </is>
+      </c>
       <c r="C243" t="inlineStr">
         <is>
           <t>DEUMUARAMA DISTRDELOVAT</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>621,892</t>
+        </is>
+      </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>621.8920000000001</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -16685,7 +17021,11 @@
       <c r="P243" t="n">
         <v>5</v>
       </c>
-      <c r="Q243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>AES 85302 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R243" t="inlineStr">
         <is>
           <t>1726541 01.20264247833541 - MUNICIPIO DE UMUARAMA</t>
@@ -16693,12 +17033,20 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T243" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>⚠ AE '085302' em múltiplos projetos: 1726388, 1726541</t>
+        </is>
+      </c>
       <c r="U243" t="inlineStr"/>
-      <c r="V243" t="inlineStr"/>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85302 4600026463 HAGAP.pdf', 'ae': '085302'}]</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -16706,15 +17054,23 @@
           <t>1726890</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>085301</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
           <t>DETERRABOA JDSENA</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>406,703</t>
+        </is>
+      </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>406.703</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -16751,7 +17107,11 @@
       <c r="P244" t="n">
         <v>5</v>
       </c>
-      <c r="Q244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>AES 85301 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr">
         <is>
           <t>1726890 01.20264225253150 - MUNICIPIO DE TERRA BOA 03.08</t>
@@ -16759,12 +17119,20 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T244" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>⚠ AE '085301' em múltiplos projetos: 1726332, 1726890, 1730222</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr"/>
-      <c r="V244" t="inlineStr"/>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85301 4600026463 HAGAP.pdf', 'ae': '085301'}]</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16772,15 +17140,23 @@
           <t>1727335</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>085417</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
           <t>DEMOREIRASALES MORADADOSOLJD</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>338,643</t>
+        </is>
+      </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>338.643</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -16817,7 +17193,11 @@
       <c r="P245" t="n">
         <v>5</v>
       </c>
-      <c r="Q245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>AES 85417 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R245" t="inlineStr">
         <is>
           <t>1727335 01.20264269641920 - MUNICIPIO DE MOREIRA SALES 10.08</t>
@@ -16825,12 +17205,20 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T245" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>⚠ AE '085417' em múltiplos projetos: 1727335, 1730642I</t>
+        </is>
+      </c>
       <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr"/>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85417 4600026463 HAGAP.pdf', 'ae': '085417'}]</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16838,15 +17226,23 @@
           <t>1730222</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>085301</t>
+        </is>
+      </c>
       <c r="C246" t="inlineStr">
         <is>
           <t>ESTRADA FUMAÇA - XAMBRE</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>406,703</t>
+        </is>
+      </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>406.703</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -16858,7 +17254,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>R$28.896,74</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -16879,7 +17279,11 @@
       <c r="P246" t="n">
         <v>3</v>
       </c>
-      <c r="Q246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>AES 85301 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R246" t="inlineStr">
         <is>
           <t>1730222 01.20263660657526 - MARCELO MENDES DE OLIVEIRA 05.08</t>
@@ -16887,12 +17291,20 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T246" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>⚠ AE '085301' em múltiplos projetos: 1726332, 1726890, 1730222</t>
+        </is>
+      </c>
       <c r="U246" t="inlineStr"/>
-      <c r="V246" t="inlineStr"/>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85301 4600026463 HAGAP.pdf', 'ae': '085301'}]</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16962,15 +17374,23 @@
           <t>1730761</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>085416</t>
+        </is>
+      </c>
       <c r="C248" t="inlineStr">
         <is>
           <t>MAICON LUIZ WATHIER</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>283,120</t>
+        </is>
+      </c>
       <c r="E248" t="n">
-        <v>0</v>
+        <v>283.12</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -16982,7 +17402,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>R$17.270,31</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -17003,7 +17427,11 @@
       <c r="P248" t="n">
         <v>4</v>
       </c>
-      <c r="Q248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>AES 85416 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R248" t="inlineStr">
         <is>
           <t>1730761 -SE em CIANORTE</t>
@@ -17011,12 +17439,20 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T248" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>⚠ AE '085416' em múltiplos projetos: 1730761, 1730908</t>
+        </is>
+      </c>
       <c r="U248" t="inlineStr"/>
-      <c r="V248" t="inlineStr"/>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85416 4600026463 HAGAP.pdf', 'ae': '085416'}]</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17024,15 +17460,23 @@
           <t>1730908</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>085416</t>
+        </is>
+      </c>
       <c r="C249" t="inlineStr">
         <is>
           <t>CIANORTE</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>283,120</t>
+        </is>
+      </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>283.12</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -17044,7 +17488,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>R$17.270,31</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -17065,7 +17513,11 @@
       <c r="P249" t="n">
         <v>3</v>
       </c>
-      <c r="Q249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>AES 85416 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R249" t="inlineStr">
         <is>
           <t>1730908 - SE em CIANORTE</t>
@@ -17073,12 +17525,20 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T249" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>⚠ AE '085416' em múltiplos projetos: 1730761, 1730908</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr"/>
-      <c r="V249" t="inlineStr"/>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85416 4600026463 HAGAP.pdf', 'ae': '085416'}]</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17288,6 +17748,1452 @@
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1710220</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>085297</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>29,740</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>R$2.270,94</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J254" t="b">
+        <v>0</v>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>AES 85297 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr"/>
+      <c r="U254" t="inlineStr"/>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85297 4600026463 HAGAP.pdf', 'ae': '085297'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1689263</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>085300</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>199,911</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>199.911</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>R$15.265,20</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J255" t="b">
+        <v>0</v>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>AES 85300 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>⚠ AE '085300' em múltiplos projetos: 1689263, 1689264</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr"/>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85300 4600026463 HAGAP.pdf', 'ae': '085300'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1689264</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>085300</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>199,911</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>199.911</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>R$15.265,20</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J256" t="b">
+        <v>0</v>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>AES 85300 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>⚠ AE '085300' em múltiplos projetos: 1689263, 1689264</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr"/>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85300 4600026463 HAGAP.pdf', 'ae': '085300'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1730642I</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>085417</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>338,643</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>338.643</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>R$20.657,21</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J257" t="b">
+        <v>0</v>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>AES 85417 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>⚠ AE '085417' em múltiplos projetos: 1727335, 1730642I</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr"/>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85417 4600026463 HAGAP.pdf', 'ae': '085417'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1590713</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>UMUARAMA</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J258" t="b">
+        <v>0</v>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>1590713 - RA</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr"/>
+      <c r="U258" t="inlineStr"/>
+      <c r="V258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1595636</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>CRO</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J259" t="b">
+        <v>0</v>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>1595636 R.A</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr"/>
+      <c r="U259" t="inlineStr"/>
+      <c r="V259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1721595</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>OPÇÃOPOROBRAPARTICULAR</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>R$16.337,54</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J260" t="b">
+        <v>0</v>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>1721595 01.20263838195656 - JAIR ZAGO 13.08</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr"/>
+      <c r="U260" t="inlineStr"/>
+      <c r="V260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1727322</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>02.06.2027</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J261" t="b">
+        <v>0</v>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>1727322 01.20264255937590 - MANOEL ROBERTO DA SILVA 17.08</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="inlineStr"/>
+      <c r="V261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1727529</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>03.11.2026</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J262" t="b">
+        <v>0</v>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>1727529 01.20264295894772 - GILMAR JOSUE GALBIATTI 17.08</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr"/>
+      <c r="V262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1729828</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>RESPONDIDA VALIDADEDEOARÇAMENTO</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>13/08/26</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J263" t="b">
+        <v>0</v>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>1729828 01.20264403643764 - DAYANE SALVIANO SANTANA 13.08</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr"/>
+      <c r="U263" t="inlineStr"/>
+      <c r="V263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1731564</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>TAPIRA</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J264" t="b">
+        <v>0</v>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>1731564 UC 17399688_CTO 8940815175_SS 20264655727975</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr"/>
+      <c r="U264" t="inlineStr"/>
+      <c r="V264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1731653</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J265" t="b">
+        <v>0</v>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>1731653 UC 98470507_CTO 8940843230_ SS 20264619700402</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr"/>
+      <c r="U265" t="inlineStr"/>
+      <c r="V265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1713223</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J266" t="b">
+        <v>0</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr"/>
+      <c r="U266" t="inlineStr"/>
+      <c r="V266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1714729I</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J267" t="b">
+        <v>1</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="n">
+        <v>1</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr"/>
+      <c r="U267" t="inlineStr"/>
+      <c r="V267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1712550</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J268" t="b">
+        <v>0</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr"/>
+      <c r="U268" t="inlineStr"/>
+      <c r="V268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1691534</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J269" t="b">
+        <v>0</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr"/>
+      <c r="U269" t="inlineStr"/>
+      <c r="V269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1722169</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J270" t="b">
+        <v>0</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="inlineStr"/>
+      <c r="V270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1713626I</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J271" t="b">
+        <v>0</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr"/>
+      <c r="U271" t="inlineStr"/>
+      <c r="V271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1709486</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J272" t="b">
+        <v>0</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr"/>
+      <c r="U272" t="inlineStr"/>
+      <c r="V272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1713656I</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J273" t="b">
+        <v>0</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr"/>
+      <c r="U273" t="inlineStr"/>
+      <c r="V273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1715201I</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J274" t="b">
+        <v>0</v>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="n">
+        <v>1</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr"/>
+      <c r="U274" t="inlineStr"/>
+      <c r="V274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1715955I</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J275" t="b">
+        <v>0</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr"/>
+      <c r="U275" t="inlineStr"/>
+      <c r="V275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1715816C</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J276" t="b">
+        <v>0</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr"/>
+      <c r="U276" t="inlineStr"/>
+      <c r="V276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1715816I</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J277" t="b">
+        <v>0</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr"/>
+      <c r="U277" t="inlineStr"/>
+      <c r="V277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>1718561</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J278" t="b">
+        <v>0</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="n">
+        <v>1</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr"/>
+      <c r="U278" t="inlineStr"/>
+      <c r="V278" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V278"/>
+  <dimension ref="A1:V280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,11 +575,15 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -599,7 +603,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -662,10 +666,14 @@
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -727,7 +735,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -743,11 +751,15 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -767,7 +779,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -813,7 +825,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,7 +911,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -997,11 +1009,15 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1021,7 +1037,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1161,11 +1177,15 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1185,7 +1205,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1399,7 +1419,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1477,7 +1497,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1555,7 +1575,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4253,7 +4273,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4343,7 +4363,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4433,7 +4453,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4523,7 +4543,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4613,7 +4633,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4703,7 +4723,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5235,11 +5255,15 @@
       <c r="J58" t="b">
         <v>0</v>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -5259,7 +5283,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6083,11 +6107,15 @@
       <c r="J68" t="b">
         <v>0</v>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -6107,7 +6135,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -19194,6 +19222,106 @@
       <c r="U278" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1658892</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J279" t="b">
+        <v>0</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr"/>
+      <c r="U279" t="inlineStr"/>
+      <c r="V279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1710329</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J280" t="b">
+        <v>0</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr"/>
+      <c r="U280" t="inlineStr"/>
+      <c r="V280" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V280"/>
+  <dimension ref="A1:V282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6669,11 +6669,15 @@
       <c r="J75" t="b">
         <v>0</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -6689,7 +6693,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -19322,6 +19326,106 @@
       <c r="U280" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1675032C</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J281" t="b">
+        <v>0</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr"/>
+      <c r="U281" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1675032I</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J282" t="b">
+        <v>0</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="n">
+        <v>1</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr"/>
+      <c r="U282" t="inlineStr"/>
+      <c r="V282" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V282"/>
+  <dimension ref="A1:V288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,7 +559,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4474,16 +4474,20 @@
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4573,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4663,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4995,24 +4999,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="n">
         <v>4</v>
@@ -5575,7 +5587,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5661,7 +5673,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -11715,7 +11727,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11793,7 +11805,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13694,7 +13706,11 @@
           <t>1706327</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>085036</t>
+        </is>
+      </c>
       <c r="C192" t="inlineStr">
         <is>
           <t>ARAPUA</t>
@@ -13708,9 +13724,21 @@
       <c r="E192" t="n">
         <v>80.63500000000001</v>
       </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>R$228.421,85</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -13731,7 +13759,11 @@
       <c r="P192" t="n">
         <v>5</v>
       </c>
-      <c r="Q192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>AES 85036 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr">
         <is>
           <t>1706327</t>
@@ -13739,12 +13771,16 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85036 4600026463 HAGAP.pdf', 'ae': '085036'}]</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13752,7 +13788,11 @@
           <t>1706336</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>085044</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>E M</t>
@@ -13766,9 +13806,21 @@
       <c r="E193" t="n">
         <v>140.125</v>
       </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>R$318.727,55</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -13789,7 +13841,11 @@
       <c r="P193" t="n">
         <v>10</v>
       </c>
-      <c r="Q193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>AES 85044 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr">
         <is>
           <t>1706336</t>
@@ -13797,12 +13853,16 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85044 4600026463 HAGAP.pdf', 'ae': '085044'}]</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13810,7 +13870,11 @@
           <t>1711120</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>085043</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>NOVA TEBAS</t>
@@ -13824,9 +13888,21 @@
       <c r="E194" t="n">
         <v>103.84</v>
       </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>R$261.193,88</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -13847,7 +13923,11 @@
       <c r="P194" t="n">
         <v>6</v>
       </c>
-      <c r="Q194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>AES 85043 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
           <t>1711120</t>
@@ -13855,12 +13935,16 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85043 4600026463 HAGAP.pdf', 'ae': '085043'}]</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13868,15 +13952,23 @@
           <t>1711629</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>085079</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>DEASCHORK AZEVEDO</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>197,739</t>
+        </is>
+      </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>197.739</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -13888,7 +13980,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>R$13.482,28</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -13909,7 +14005,11 @@
       <c r="P195" t="n">
         <v>3</v>
       </c>
-      <c r="Q195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>AES 85079 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R195" t="inlineStr">
         <is>
           <t>1711629 01.20263195647434 - ALESSANDRO SAMPAIO RIBEIRO 20.07</t>
@@ -13917,12 +14017,20 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T195" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>⚠ AE '085079' em múltiplos projetos: 1711629, 1711788, 1713681</t>
+        </is>
+      </c>
       <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85079 4600026463 HAGAP.pdf', 'ae': '085079'}]</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13930,15 +14038,23 @@
           <t>1711788</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>085079</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>ESPERANÇA NOVA</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>197,739</t>
+        </is>
+      </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>197.739</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -13950,7 +14066,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>R$13.482,28</t>
+        </is>
+      </c>
       <c r="I196" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -13971,7 +14091,11 @@
       <c r="P196" t="n">
         <v>3</v>
       </c>
-      <c r="Q196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>AES 85079 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R196" t="inlineStr">
         <is>
           <t>1711788 01.20263240861110 - ASSOCIACAO COMUNITARIA TERRA BOA 20.07</t>
@@ -13979,12 +14103,20 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>⚠ AE '085079' em múltiplos projetos: 1711629, 1711788, 1713681</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85079 4600026463 HAGAP.pdf', 'ae': '085079'}]</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13992,15 +14124,23 @@
           <t>1713681</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>085079</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>DEASCHORK AZEVEDO</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>197,739</t>
+        </is>
+      </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>197.739</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -14012,7 +14152,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>R$13.482,28</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14033,7 +14177,11 @@
       <c r="P197" t="n">
         <v>3</v>
       </c>
-      <c r="Q197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>AES 85079 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
           <t>1713681 01.20263343447907 - JHIMY KENEDY SOUZA FERRARI 20.07</t>
@@ -14041,12 +14189,20 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>⚠ AE '085079' em múltiplos projetos: 1711629, 1711788, 1713681</t>
+        </is>
+      </c>
       <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85079 4600026463 HAGAP.pdf', 'ae': '085079'}]</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14054,7 +14210,11 @@
           <t>1716557</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>085155</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>CIANORTE</t>
@@ -14068,9 +14228,21 @@
       <c r="E198" t="n">
         <v>825.664</v>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>R$219.995,37</t>
+        </is>
+      </c>
       <c r="I198" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14091,7 +14263,11 @@
       <c r="P198" t="n">
         <v>6</v>
       </c>
-      <c r="Q198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>AES 85155 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R198" t="inlineStr">
         <is>
           <t>1716557 - LDNU335802024   - croqui 3. Cianorte</t>
@@ -14099,12 +14275,20 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>⚠ AE '085155' em múltiplos projetos: 1716557, 1716612</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr"/>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85155 4600026463 HAGAP.pdf', 'ae': '085155'}]</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14112,7 +14296,11 @@
           <t>1716612</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>085155</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>CIANORTE</t>
@@ -14126,9 +14314,21 @@
       <c r="E199" t="n">
         <v>32.42</v>
       </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>R$219.995,37</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14149,7 +14349,11 @@
       <c r="P199" t="n">
         <v>4</v>
       </c>
-      <c r="Q199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>AES 85155 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R199" t="inlineStr">
         <is>
           <t>1716612  -LDNU335802024 - croqui 3. Cianorte</t>
@@ -14157,12 +14361,20 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>⚠ AE '085155' em múltiplos projetos: 1716557, 1716612</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85155 4600026463 HAGAP.pdf', 'ae': '085155'}]</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14170,7 +14382,11 @@
           <t>1718441</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>085128</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
           <t>WESLEY ORTIZ DE OLIVEIRA</t>
@@ -14184,9 +14400,21 @@
       <c r="E200" t="n">
         <v>942.003</v>
       </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>R$102.545,06</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14207,7 +14435,11 @@
       <c r="P200" t="n">
         <v>6</v>
       </c>
-      <c r="Q200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>AES 85128 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
           <t>1718441 -LDNU335802024 - croqui 3. Cianorte</t>
@@ -14215,12 +14447,16 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85128 4600026463 HAGAP.pdf', 'ae': '085128'}]</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14228,15 +14464,23 @@
           <t>1719077</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>085082</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>821,638</t>
+        </is>
+      </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>821.638</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -14248,7 +14492,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>R$55.391,23</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14269,7 +14517,11 @@
       <c r="P201" t="n">
         <v>3</v>
       </c>
-      <c r="Q201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>AES 85082 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R201" t="inlineStr">
         <is>
           <t>1719077 01.20263579349056 - SALVADOR ZANOLI 18.09</t>
@@ -14277,12 +14529,20 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>⚠ AE '085082' em múltiplos projetos: 1719077, 1724174, 1724550, 1726318, 1729397I</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85082 4600026463 HAGAP.pdf', 'ae': '085082'}]</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14290,15 +14550,23 @@
           <t>1721898</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
           <t>SILVA AZEVEDO</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>2052.45</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -14310,7 +14578,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
       <c r="I202" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14331,7 +14603,11 @@
       <c r="P202" t="n">
         <v>3</v>
       </c>
-      <c r="Q202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
           <t>1721898 01.20263889505744 - EPR PARANA S.A 16.09</t>
@@ -14339,12 +14615,20 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr"/>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14418,15 +14702,23 @@
           <t>1724053</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
       <c r="C204" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>2052.45</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -14438,7 +14730,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
       <c r="I204" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14459,7 +14755,11 @@
       <c r="P204" t="n">
         <v>3</v>
       </c>
-      <c r="Q204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr">
         <is>
           <t>1724053 01.20263997605660 - JESSICA FERNANDA BONIFACIO DOS SANTOS 24.07</t>
@@ -14467,12 +14767,20 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T204" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr"/>
-      <c r="V204" t="inlineStr"/>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14480,15 +14788,23 @@
           <t>1724174</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>085082</t>
+        </is>
+      </c>
       <c r="C205" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>821,638</t>
+        </is>
+      </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>821.638</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -14525,7 +14841,11 @@
       <c r="P205" t="n">
         <v>4</v>
       </c>
-      <c r="Q205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>AES 85082 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R205" t="inlineStr">
         <is>
           <t>1724174 01.20264077495618 - SECRETARIA DE ESTADO DA EDUCACAO SEED 21.09</t>
@@ -14533,12 +14853,20 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T205" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>⚠ AE '085082' em múltiplos projetos: 1719077, 1724174, 1724550, 1726318, 1729397I</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr"/>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85082 4600026463 HAGAP.pdf', 'ae': '085082'}]</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14546,15 +14874,23 @@
           <t>1724491</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>085153</t>
+        </is>
+      </c>
       <c r="C206" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>321,312</t>
+        </is>
+      </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>321.312</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -14566,7 +14902,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>R$24.535,37</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14591,7 +14931,11 @@
       <c r="P206" t="n">
         <v>4</v>
       </c>
-      <c r="Q206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>AES 85153 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
           <t>1724491 01.20264110172007 - GILMAR ALEIXO 23.09</t>
@@ -14599,12 +14943,20 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>pasta, medicao</t>
-        </is>
-      </c>
-      <c r="T206" t="inlineStr"/>
+          <t>pasta, medicao, ae</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>⚠ AE '085153' em múltiplos projetos: 1724491, 1725686</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr"/>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85153 4600026463 HAGAP.pdf', 'ae': '085153'}]</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14612,15 +14964,23 @@
           <t>1724537</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>085152</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
           <t>DEASCHORK AZEVEDO</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>284,315</t>
+        </is>
+      </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>284.315</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -14632,7 +14992,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>R$19.215,26</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14653,7 +15017,11 @@
       <c r="P207" t="n">
         <v>3</v>
       </c>
-      <c r="Q207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>AES 85152 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
           <t>1724537 01.20263968582955 - AGUINEL FERREIRA DA CRUZ 03.08</t>
@@ -14661,12 +15029,20 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T207" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>⚠ AE '085152' em múltiplos projetos: 1724537, 1725260, 1726324, 1728642</t>
+        </is>
+      </c>
       <c r="U207" t="inlineStr"/>
-      <c r="V207" t="inlineStr"/>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85152 4600026463 HAGAP.pdf', 'ae': '085152'}]</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14674,15 +15050,23 @@
           <t>1724550</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>085082</t>
+        </is>
+      </c>
       <c r="C208" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>821,638</t>
+        </is>
+      </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>821.638</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -14694,7 +15078,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>R$55.391,23</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14715,7 +15103,11 @@
       <c r="P208" t="n">
         <v>3</v>
       </c>
-      <c r="Q208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>AES 85082 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr">
         <is>
           <t>1724550 01.20264098016709 - ASSOCIACAO DO NUCLEO DE PRODUCAO DOS IDOSOS DE ALTONIA PR 3 IDADE 18.09</t>
@@ -14723,12 +15115,20 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T208" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>⚠ AE '085082' em múltiplos projetos: 1719077, 1724174, 1724550, 1726318, 1729397I</t>
+        </is>
+      </c>
       <c r="U208" t="inlineStr"/>
-      <c r="V208" t="inlineStr"/>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85082 4600026463 HAGAP.pdf', 'ae': '085082'}]</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14736,15 +15136,23 @@
           <t>1724558</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
       <c r="C209" t="inlineStr">
         <is>
           <t>SILVA AZEVEDO</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>2052.45</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -14756,7 +15164,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14777,7 +15189,11 @@
       <c r="P209" t="n">
         <v>4</v>
       </c>
-      <c r="Q209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
           <t>1724558 01.20263889412776 - EPR PARANA S.A 19.05.2027</t>
@@ -14785,12 +15201,20 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T209" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
       <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14798,15 +15222,23 @@
           <t>1725260</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>085152</t>
+        </is>
+      </c>
       <c r="C210" t="inlineStr">
         <is>
           <t>ANUNCIACAO AZEVEDO</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>284,315</t>
+        </is>
+      </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>284.315</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -14847,7 +15279,11 @@
       <c r="P210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>AES 85152 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
           <t>1725260 01.20264163756882 - CONSTRUTORA RVA LTDA 27.07</t>
@@ -14855,12 +15291,20 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>pasta, medicao</t>
-        </is>
-      </c>
-      <c r="T210" t="inlineStr"/>
+          <t>pasta, medicao, ae</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>⚠ AE '085152' em múltiplos projetos: 1724537, 1725260, 1726324, 1728642</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr"/>
-      <c r="V210" t="inlineStr"/>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85152 4600026463 HAGAP.pdf', 'ae': '085152'}]</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14868,15 +15312,23 @@
           <t>1725686</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>085153</t>
+        </is>
+      </c>
       <c r="C211" t="inlineStr">
         <is>
           <t>CARVALHO AZEVEDO</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>321,312</t>
+        </is>
+      </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>321.312</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -14888,7 +15340,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>R$24.535,37</t>
+        </is>
+      </c>
       <c r="I211" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14909,7 +15365,11 @@
       <c r="P211" t="n">
         <v>4</v>
       </c>
-      <c r="Q211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>AES 85153 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R211" t="inlineStr">
         <is>
           <t>1725686 01.20264132155190 - JOAO DA SILVA NETO 23.09</t>
@@ -14917,12 +15377,20 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T211" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>⚠ AE '085153' em múltiplos projetos: 1724491, 1725686</t>
+        </is>
+      </c>
       <c r="U211" t="inlineStr"/>
-      <c r="V211" t="inlineStr"/>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85153 4600026463 HAGAP.pdf', 'ae': '085153'}]</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14930,15 +15398,23 @@
           <t>1726318</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>085082</t>
+        </is>
+      </c>
       <c r="C212" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>821,638</t>
+        </is>
+      </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>821.638</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -14950,7 +15426,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>R$55.391,23</t>
+        </is>
+      </c>
       <c r="I212" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -14971,7 +15451,11 @@
       <c r="P212" t="n">
         <v>3</v>
       </c>
-      <c r="Q212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>AES 85082 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R212" t="inlineStr">
         <is>
           <t>1726318 01.20264173095321 - VIVIANE FERREIRA CAMILO GONZAGA 22.09</t>
@@ -14979,12 +15463,20 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>⚠ AE '085082' em múltiplos projetos: 1719077, 1724174, 1724550, 1726318, 1729397I</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr"/>
-      <c r="V212" t="inlineStr"/>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85082 4600026463 HAGAP.pdf', 'ae': '085082'}]</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14992,15 +15484,23 @@
           <t>1726324</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>085152</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>284,315</t>
+        </is>
+      </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>284.315</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -15012,7 +15512,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>R$19.215,26</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15033,7 +15537,11 @@
       <c r="P213" t="n">
         <v>3</v>
       </c>
-      <c r="Q213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>AES 85152 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
           <t>1726324 01.20264187424019 - SILVIO YNAMURA 31.07</t>
@@ -15041,12 +15549,20 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>⚠ AE '085152' em múltiplos projetos: 1724537, 1725260, 1726324, 1728642</t>
+        </is>
+      </c>
       <c r="U213" t="inlineStr"/>
-      <c r="V213" t="inlineStr"/>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85152 4600026463 HAGAP.pdf', 'ae': '085152'}]</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15054,15 +15570,23 @@
           <t>1726942</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>085154</t>
+        </is>
+      </c>
       <c r="C214" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>73,869</t>
+        </is>
+      </c>
       <c r="E214" t="n">
-        <v>0</v>
+        <v>73.869</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -15099,7 +15623,11 @@
       <c r="P214" t="n">
         <v>3</v>
       </c>
-      <c r="Q214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>AES 85154 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
           <t>1726942 01.20264264580530 - AFONSO DE OLIVEIRA BERTONCELO 17.11</t>
@@ -15107,12 +15635,16 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr"/>
-      <c r="V214" t="inlineStr"/>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85154 4600026463 HAGAP.pdf', 'ae': '085154'}]</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15120,19 +15652,39 @@
           <t>1728642</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>085152</t>
+        </is>
+      </c>
       <c r="C215" t="inlineStr">
         <is>
           <t>GIOVANNI M CARVALHO</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>284,315</t>
+        </is>
+      </c>
       <c r="E215" t="n">
-        <v>0</v>
-      </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
+        <v>284.315</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>R$19.215,26</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15153,7 +15705,11 @@
       <c r="P215" t="n">
         <v>3</v>
       </c>
-      <c r="Q215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>AES 85152 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
           <t>1728642 01.20264308973713 - EVANDO APARECIDO BORGES SILVA 30.07</t>
@@ -15161,12 +15717,20 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>⚠ AE '085152' em múltiplos projetos: 1724537, 1725260, 1726324, 1728642</t>
+        </is>
+      </c>
       <c r="U215" t="inlineStr"/>
-      <c r="V215" t="inlineStr"/>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85152 4600026463 HAGAP.pdf', 'ae': '085152'}]</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15726,15 +16290,23 @@
           <t>1722845</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
       <c r="C226" t="inlineStr">
         <is>
           <t>SILVA AZEVEDO</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>2052.45</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -15746,7 +16318,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
       <c r="I226" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15767,7 +16343,11 @@
       <c r="P226" t="n">
         <v>4</v>
       </c>
-      <c r="Q226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr">
         <is>
           <t>1722845 01.20263890080326 - EPR PARANA S.A 19.05.2027</t>
@@ -15775,12 +16355,20 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T226" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
       <c r="U226" t="inlineStr"/>
-      <c r="V226" t="inlineStr"/>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15788,15 +16376,23 @@
           <t>1723691</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
       <c r="C227" t="inlineStr">
         <is>
           <t>CARVALHO AZEVEDO</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>2052.45</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -15808,7 +16404,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -15829,7 +16429,11 @@
       <c r="P227" t="n">
         <v>3</v>
       </c>
-      <c r="Q227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr">
         <is>
           <t>1723691 01.20264027799054 - ASSOCIACAO ASSISTENCIAL E PROMOCIONAL CASA DA PAZ 16.09</t>
@@ -15837,12 +16441,20 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
       <c r="U227" t="inlineStr"/>
-      <c r="V227" t="inlineStr"/>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -18693,24 +19305,32 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>29.06.2026</t>
+        </is>
+      </c>
       <c r="N268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P268" t="n">
         <v>0</v>
@@ -18804,10 +19424,14 @@
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -19426,6 +20050,402 @@
       <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1724051I</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>2052.45</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J283" t="b">
+        <v>0</v>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr"/>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr"/>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1729112I</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>085078</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2.052,450</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>2052.45</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>R$151.495,34</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J284" t="b">
+        <v>0</v>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>AES 85078 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr"/>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>⚠ AE '085078' em múltiplos projetos: 1721898, 1724053, 1724558, 1722845, 1723691, 1724051I, 1729112I</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr"/>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85078 4600026463 HAGAP.pdf', 'ae': '085078'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1729397I</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>085082</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>821,638</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>821.638</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>R$55.391,23</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J285" t="b">
+        <v>0</v>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>AES 85082 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr"/>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>⚠ AE '085082' em múltiplos projetos: 1719077, 1724174, 1724550, 1726318, 1729397I</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr"/>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85082 4600026463 HAGAP.pdf', 'ae': '085082'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1728328</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J286" t="b">
+        <v>0</v>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>1728328 01.20264368975557 - ROBERSON DA SILVA FABIANO 20.08</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr"/>
+      <c r="U286" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1698781</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J287" t="b">
+        <v>0</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr"/>
+      <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>1660062C</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J288" t="b">
+        <v>0</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr"/>
+      <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V288"/>
+  <dimension ref="A1:V336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,7 +645,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2851,7 +2851,11 @@
           <t>083980</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>1.080,951</t>
@@ -2867,7 +2871,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2897,17 +2901,21 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>AES 83980 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1713260 01.20263351732713 - CELIA LUIZA IZELLI DE OLIVEIRA 12.08</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>ae, medicao</t>
+          <t>ae, medicao, pasta</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -2953,7 +2961,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3023,7 +3031,11 @@
           <t>083980</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ESQUERDAOLHANDODEFRENTE</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>1.080,951</t>
@@ -3039,7 +3051,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3065,17 +3077,21 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>AES 83980 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1717380 01.20263562531487 - AMERICO HENRIQUES FRANCISCO</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, pasta</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3101,7 +3117,11 @@
           <t>083980</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RDR DE XAMBRE</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>1.080,951</t>
@@ -3117,7 +3137,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3143,17 +3163,21 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>AES 83980 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1719154 -  1730222 01.20263660657526 - MARCELO MENDES DE OLIVEIRA 05.08 NÃO SERA EXECUTADO</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, pasta</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3179,7 +3203,11 @@
           <t>083980</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MARILUZ</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>1.080,951</t>
@@ -3195,7 +3223,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3225,17 +3253,21 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>AES 83980 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1717166 01.20263506068693 - TALIA CARDOSO DA SILVA ARAGAO</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>ae, medicao</t>
+          <t>ae, medicao, pasta</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3445,7 +3477,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3531,7 +3563,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3597,7 +3629,11 @@
           <t>084013</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ARAUJO AZEVEDO</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>253,608</t>
@@ -3613,7 +3649,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3647,17 +3683,21 @@
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>AES 84013 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1720721 01.20263803172857 - ABILIO LOPES FERNANDES</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>ae, medicao</t>
+          <t>ae, medicao, pasta</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3699,7 +3739,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3781,7 +3821,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3859,7 +3899,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3925,7 +3965,11 @@
           <t>084025</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MOREIRA SALES</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>4.244,330</t>
@@ -3941,7 +3985,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3967,17 +4011,21 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>AES 84025 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1722165 - ALNC327072022 - Substituicao do BRT 81584RT326</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, pasta</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4023,7 +4071,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4113,7 +4161,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4191,7 +4239,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4813,7 +4861,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4903,7 +4951,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4989,7 +5037,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5083,7 +5131,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5165,7 +5213,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5251,7 +5299,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5337,7 +5385,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5423,7 +5471,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5449,7 +5497,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5505,7 +5553,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5587,7 +5635,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5673,7 +5721,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7233,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8435,13 +8483,25 @@
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CAA</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
         <v>0</v>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>04.06.2023</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
@@ -8465,13 +8525,17 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1520612 CIT</t>
+        </is>
+      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>medicao</t>
+          <t>medicao, pasta</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -9325,14 +9389,30 @@
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CONTRATODEM</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
         <v>0</v>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>R$139,89</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -9355,13 +9435,17 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>1677314 01.20252477868689 - LUIZ CARLOS BARBOSA JUNIOR 12.03.27</t>
+        </is>
+      </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>medicao</t>
+          <t>medicao, pasta</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -10115,11 +10199,11 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10127,12 +10211,16 @@
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
       <c r="N137" t="n">
         <v>1</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -10805,7 +10893,7 @@
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -11137,14 +11225,30 @@
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CONTRATODEM</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
         <v>0</v>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>R$139,89</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -11167,13 +11271,17 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>1677316 01.20252477868689 - LUIZ CARLOS BARBOSA JUNIOR 12.03.27</t>
+        </is>
+      </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>medicao</t>
+          <t>medicao, pasta</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -12069,7 +12177,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12159,7 +12267,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12245,7 +12353,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12271,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
@@ -12331,7 +12439,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12421,7 +12529,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -12507,7 +12615,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -12533,7 +12641,7 @@
         <v>0</v>
       </c>
       <c r="P176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
@@ -12701,7 +12809,7 @@
         <v>0</v>
       </c>
       <c r="P178" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -13049,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="P182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -14063,7 +14171,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14515,7 +14623,7 @@
         <v>0</v>
       </c>
       <c r="P201" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
@@ -14679,7 +14787,7 @@
         <v>0</v>
       </c>
       <c r="P203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
@@ -15363,7 +15471,7 @@
         <v>0</v>
       </c>
       <c r="P211" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
@@ -15449,7 +15557,7 @@
         <v>0</v>
       </c>
       <c r="P212" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -17215,7 +17323,7 @@
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr">
@@ -17835,7 +17943,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -17921,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="P246" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -18155,7 +18263,7 @@
         <v>0</v>
       </c>
       <c r="P249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -18419,7 +18527,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18493,7 +18601,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -18571,7 +18679,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -18649,7 +18757,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -18814,15 +18922,23 @@
           <t>1721595</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>085592</t>
+        </is>
+      </c>
       <c r="C260" t="inlineStr">
         <is>
           <t>OPÇÃOPOROBRAPARTICULAR</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>151,097</t>
+        </is>
+      </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>151.097</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -18857,9 +18973,13 @@
         <v>0</v>
       </c>
       <c r="P260" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q260" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>AES 85592 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R260" t="inlineStr">
         <is>
           <t>1721595 01.20263838195656 - JAIR ZAGO 13.08</t>
@@ -18867,12 +18987,20 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>⚠ AE '085592' em múltiplos projetos: 1721595, 1727322, 1727529, 1729828</t>
+        </is>
+      </c>
       <c r="U260" t="inlineStr"/>
-      <c r="V260" t="inlineStr"/>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85592 4600026463 HAGAP.pdf', 'ae': '085592'}]</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18880,15 +19008,23 @@
           <t>1727322</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>085592</t>
+        </is>
+      </c>
       <c r="C261" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>151,097</t>
+        </is>
+      </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>151.097</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -18900,7 +19036,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>R$11.250,94</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -18921,7 +19061,11 @@
       <c r="P261" t="n">
         <v>4</v>
       </c>
-      <c r="Q261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>AES 85592 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R261" t="inlineStr">
         <is>
           <t>1727322 01.20264255937590 - MANOEL ROBERTO DA SILVA 17.08</t>
@@ -18929,12 +19073,20 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T261" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>⚠ AE '085592' em múltiplos projetos: 1721595, 1727322, 1727529, 1729828</t>
+        </is>
+      </c>
       <c r="U261" t="inlineStr"/>
-      <c r="V261" t="inlineStr"/>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85592 4600026463 HAGAP.pdf', 'ae': '085592'}]</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18942,15 +19094,23 @@
           <t>1727529</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>085592</t>
+        </is>
+      </c>
       <c r="C262" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>151,097</t>
+        </is>
+      </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>151.097</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -18962,7 +19122,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>R$11.250,94</t>
+        </is>
+      </c>
       <c r="I262" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -18983,7 +19147,11 @@
       <c r="P262" t="n">
         <v>3</v>
       </c>
-      <c r="Q262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>AES 85592 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R262" t="inlineStr">
         <is>
           <t>1727529 01.20264295894772 - GILMAR JOSUE GALBIATTI 17.08</t>
@@ -18991,12 +19159,20 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T262" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>⚠ AE '085592' em múltiplos projetos: 1721595, 1727322, 1727529, 1729828</t>
+        </is>
+      </c>
       <c r="U262" t="inlineStr"/>
-      <c r="V262" t="inlineStr"/>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85592 4600026463 HAGAP.pdf', 'ae': '085592'}]</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -19004,15 +19180,23 @@
           <t>1729828</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>085592</t>
+        </is>
+      </c>
       <c r="C263" t="inlineStr">
         <is>
           <t>RESPONDIDA VALIDADEDEOARÇAMENTO</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>151,097</t>
+        </is>
+      </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>151.097</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -19024,7 +19208,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>R$11.250,94</t>
+        </is>
+      </c>
       <c r="I263" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -19045,7 +19233,11 @@
       <c r="P263" t="n">
         <v>4</v>
       </c>
-      <c r="Q263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>AES 85592 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R263" t="inlineStr">
         <is>
           <t>1729828 01.20264403643764 - DAYANE SALVIANO SANTANA 13.08</t>
@@ -19053,12 +19245,20 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T263" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>⚠ AE '085592' em múltiplos projetos: 1721595, 1727322, 1727529, 1729828</t>
+        </is>
+      </c>
       <c r="U263" t="inlineStr"/>
-      <c r="V263" t="inlineStr"/>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85592 4600026463 HAGAP.pdf', 'ae': '085592'}]</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -19507,14 +19707,30 @@
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>DECIANORTE ZONAUM</t>
+        </is>
+      </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="n">
         <v>0</v>
       </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>R$ 47.063,85</t>
+        </is>
+      </c>
       <c r="I272" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -19537,13 +19753,17 @@
         <v>0</v>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q272" t="inlineStr"/>
-      <c r="R272" t="inlineStr"/>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>1709486 01.20246775246601 MUNICIPIO DE CIANORTE 25.09.2026</t>
+        </is>
+      </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>medicao</t>
+          <t>medicao, pasta</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -20077,7 +20297,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -20155,7 +20375,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20233,7 +20453,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -20290,15 +20510,23 @@
           <t>1728328</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>085631</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>58,451</t>
+        </is>
+      </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>58.451</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -20310,7 +20538,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>R$3.565,51</t>
+        </is>
+      </c>
       <c r="I286" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -20331,7 +20563,11 @@
       <c r="P286" t="n">
         <v>3</v>
       </c>
-      <c r="Q286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>AES 85631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R286" t="inlineStr">
         <is>
           <t>1728328 01.20264368975557 - ROBERSON DA SILVA FABIANO 20.08</t>
@@ -20339,12 +20575,16 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
       <c r="U286" t="inlineStr"/>
-      <c r="V286" t="inlineStr"/>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85631 4600026463 HAGAP.pdf', 'ae': '085631'}]</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -20446,6 +20686,3818 @@
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>1704802</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J289" t="b">
+        <v>0</v>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>1704802 01.20264214863079 - ECKERT BOTELHO ODONTOLOGIA LTDA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>1724551</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>PEROLA</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J290" t="b">
+        <v>0</v>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>1724551 01.20264053691844 - MUNICIPIO DE PEROLA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr"/>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>1726320</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J291" t="b">
+        <v>0</v>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>1726320 01.20263550388248 - GABRIEL FERREIRA DE LIMA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr"/>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>1718951</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J292" t="b">
+        <v>0</v>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>1718951 01.20264175375333 - MUNICIPIO DE DOURADINA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr"/>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>1727849</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J293" t="b">
+        <v>0</v>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>1727849 01.20264337024779 - SIMONY JEREMIAS DA SILVA 27.08.2026</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr"/>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>1729300</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J294" t="b">
+        <v>0</v>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>1729300 01.20264387726193 - IGREJA MISSAO EVANGELICA A PALAVRA DA CRUZ 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr"/>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J295" t="b">
+        <v>0</v>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>1730763 01.20264544008750 - MARCIO ROGERIO DE ALMEIDA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>1731167</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>085921</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>893,851</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>893.851</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>R$59.203,65</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J296" t="b">
+        <v>0</v>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>AES 82921 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>1731167 01.20264566147161 - JOCIMAR PEREIRA MALFATO 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>⚠ AE '085921' em múltiplos projetos: 1704802, 1724551, 1726320, 1718951, 1727849, 1729300, 1730763, 1731167</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr"/>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 82921 4600026463 HAGAP.pdf', 'ae': '085921'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>1731564I</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>085593</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>156,481</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>156.481</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>R$11.948,87</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J297" t="b">
+        <v>0</v>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>AES 85593 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>⚠ AE '085593' em múltiplos projetos: 1731564I, 1731653I, 1731564C</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr"/>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85593 4600026463 HAGAP.pdf', 'ae': '085593'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>1731653I</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>085593</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>156,481</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>156.481</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>R$11.948,87</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J298" t="b">
+        <v>0</v>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>AES 85593 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>⚠ AE '085593' em múltiplos projetos: 1731564I, 1731653I, 1731564C</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr"/>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85593 4600026463 HAGAP.pdf', 'ae': '085593'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>1731564C</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>085593</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>156,481</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>156.481</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>R$11.948,87</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J299" t="b">
+        <v>0</v>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>AES 85593 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>⚠ AE '085593' em múltiplos projetos: 1731564I, 1731653I, 1731564C</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr"/>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85593 4600026463 HAGAP.pdf', 'ae': '085593'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>1729786</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>085705</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>GERONIMODASILVA AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>579,679</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>579.679</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>R$44.264,28</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J300" t="b">
+        <v>0</v>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
+      <c r="P300" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>AES 85705 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>1729786 01.20264476513815 - LUIZ ROBERTO GENTILIN 18.06.27</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr"/>
+      <c r="U300" t="inlineStr"/>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85705 4600026463 HAGAP.pdf', 'ae': '085705'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>1674093</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>085706</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>DEXAMBRE CENTRO</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>218,119</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>218.119</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>R$13.305,24</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J301" t="b">
+        <v>0</v>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="P301" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>AES 85706 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>1674093 01.20263856400182 - MUNICIPIO DE XAMBRE 21082026</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>⚠ AE '085706' em múltiplos projetos: 1674093, 1697912, 1721180, 1729668</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr"/>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85706 4600026463 HAGAP.pdf', 'ae': '085706'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>1697912</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>085706</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>DEXAMBRE CENTRO</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>218,119</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>218.119</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>R$13.305,24</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J302" t="b">
+        <v>0</v>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>AES 85706 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>1697912 01.20263856027835 - MUNICIPIO DE XAMBRE 21.08</t>
+        </is>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>⚠ AE '085706' em múltiplos projetos: 1674093, 1697912, 1721180, 1729668</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85706 4600026463 HAGAP.pdf', 'ae': '085706'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>1721180</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>085706</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>DEXAMBRE CENTRO</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>218,119</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>218.119</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>R$13.305,24</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J303" t="b">
+        <v>0</v>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="P303" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>AES 85706 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>1721180 01.20263856505679 - MUNICIPIO DE XAMBRE 21.08</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>⚠ AE '085706' em múltiplos projetos: 1674093, 1697912, 1721180, 1729668</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr"/>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85706 4600026463 HAGAP.pdf', 'ae': '085706'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1729668</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>085706</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>218,119</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>218.119</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>R$13.305,24</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J304" t="b">
+        <v>0</v>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>AES 85706 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>1729668 01.20264466723699 - VILLARES CONSTRUTORA E METALURGICA LTDA 21.08</t>
+        </is>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>⚠ AE '085706' em múltiplos projetos: 1674093, 1697912, 1721180, 1729668</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr"/>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85706 4600026463 HAGAP.pdf', 'ae': '085706'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>1726496</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>085707</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>582,915</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>582.915</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>R$42.100,83</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J305" t="b">
+        <v>0</v>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>AES 85707 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>1726496 01.20264130619957 - LUCINEIA CLAUDINO 08.10</t>
+        </is>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>⚠ AE '085707' em múltiplos projetos: 1726496, 1728055, 1730270</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr"/>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85707 4600026463 HAGAP.pdf', 'ae': '085707'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>1728055</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>085707</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>582,915</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>582.915</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>R$42.100,83</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J306" t="b">
+        <v>0</v>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>AES 85707 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>1728055 01.20264279540601 - AGNALDO RODRIGO SERVELLO 14.10</t>
+        </is>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>⚠ AE '085707' em múltiplos projetos: 1726496, 1728055, 1730270</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85707 4600026463 HAGAP.pdf', 'ae': '085707'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>1730270</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>085707</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>582,915</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>582.915</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>R$42.100,83</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J307" t="b">
+        <v>0</v>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>AES 85707 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>1730270 01.20264496639720 - ALINE DA SILVA GALHARINI 16.10</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>⚠ AE '085707' em múltiplos projetos: 1726496, 1728055, 1730270</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr"/>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85707 4600026463 HAGAP.pdf', 'ae': '085707'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>1711378</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>085767</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>DEJUSSARA CENTRO</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>175,862</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>175.862</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>R$10.727,58</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J308" t="b">
+        <v>0</v>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>AES 85767 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>1711378 01.20263138714035 - MUNICIPIO DE JUSSARA</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr"/>
+      <c r="U308" t="inlineStr"/>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85767 4600026463 HAGAP.pdf', 'ae': '085767'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>1723727</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>085922</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>720,820</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>720.8200000000001</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>R$45.853,04</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J309" t="b">
+        <v>0</v>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>AES 85922 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>1723727 01.20264027944042 - JOSE ADILSON DE OLIVEIRA DAS MERCES 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>⚠ AE '085922' em múltiplos projetos: 1723727, 1718958, 1718954, 1731508</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr"/>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85922 4600026463 HAGAP.pdf', 'ae': '085922'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>1718958</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>085922</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>720,820</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>720.8200000000001</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>R$45.853,04</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J310" t="b">
+        <v>0</v>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
+      <c r="P310" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>AES 85922 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>1718958 01.20264175164746 - MUNICIPIO DE DOURADINA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>⚠ AE '085922' em múltiplos projetos: 1723727, 1718958, 1718954, 1731508</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85922 4600026463 HAGAP.pdf', 'ae': '085922'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1718954</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>085922</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>720,820</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>720.8200000000001</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>R$45.853,04</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J311" t="b">
+        <v>0</v>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" t="n">
+        <v>0</v>
+      </c>
+      <c r="P311" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>AES 85922 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>1718954 01.20264175413399 - MUNICIPIO DE DOURADINA 24.08.2026</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>⚠ AE '085922' em múltiplos projetos: 1723727, 1718958, 1718954, 1731508</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr"/>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85922 4600026463 HAGAP.pdf', 'ae': '085922'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>1731508</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>085922</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>720,820</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>720.8200000000001</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>R$45.853,04</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J312" t="b">
+        <v>0</v>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="n">
+        <v>0</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>AES 85922 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>1731508 01.20264548465591 - JAIME LUIZ CAMACHO 28.08.2026</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>⚠ AE '085922' em múltiplos projetos: 1723727, 1718958, 1718954, 1731508</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr"/>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85922 4600026463 HAGAP.pdf', 'ae': '085922'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>1723724</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>085946</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1.705,308</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>1705.308</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>R$104.023,78</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J313" t="b">
+        <v>0</v>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>AES 85946 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>1723724 01.20264011902775 - MARCOS VINICIUS ESCUDEIRO VATRAS 24.11.2026</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>⚠ AE '085946' em múltiplos projetos: 1723724, 1718956, 1718950</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr"/>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85946 4600026463 HAGAP.pdf', 'ae': '085946'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>1718956</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>085946</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1.705,308</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>1705.308</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>R$104.023,78</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J314" t="b">
+        <v>0</v>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>AES 85946 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>1718956 01.20264175112564 - MUNICIPIO DE DOURADINA 23.10.2026</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>⚠ AE '085946' em múltiplos projetos: 1723724, 1718956, 1718950</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr"/>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85946 4600026463 HAGAP.pdf', 'ae': '085946'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1718950</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>085946</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1.705,308</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>1705.308</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>R$104.023,78</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J315" t="b">
+        <v>0</v>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>AES 85946 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>1718950 01.20264174679416 - MUNICIPIO DE DOURADINA 23.10.2026</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>⚠ AE '085946' em múltiplos projetos: 1723724, 1718956, 1718950</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr"/>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85946 4600026463 HAGAP.pdf', 'ae': '085946'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1733419I</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>085947</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>14,212</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>14.212</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>R$1.085,22</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J316" t="b">
+        <v>0</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>AES 85947 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr"/>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr"/>
+      <c r="U316" t="inlineStr"/>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85947 4600026463 HAGAP.pdf', 'ae': '085947'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>1671216C</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>085948</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>0,221</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>R$13,48</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J317" t="b">
+        <v>0</v>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>AES 85948 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr"/>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr"/>
+      <c r="U317" t="inlineStr"/>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85948 4600026463 HAGAP.pdf', 'ae': '085948'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>1734888</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>085949</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>397,368</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>397.368</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>R$30.343,02</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J318" t="b">
+        <v>0</v>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>AES 85949 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr"/>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>⚠ AE '085949' em múltiplos projetos: 1734888, 1734971</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr"/>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85949 4600026463 HAGAP.pdf', 'ae': '085949'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1734971</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>085949</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>397,368</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>397.368</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>R$30.343,02</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J319" t="b">
+        <v>0</v>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>AES 85949 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr"/>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>⚠ AE '085949' em múltiplos projetos: 1734888, 1734971</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr"/>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85949 4600026463 HAGAP.pdf', 'ae': '085949'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1722905</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J320" t="b">
+        <v>0</v>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="n">
+        <v>0</v>
+      </c>
+      <c r="O320" t="n">
+        <v>0</v>
+      </c>
+      <c r="P320" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>1722905 01.20263904965645 - SIRLEY IMPERIAL INDUSTRIA DE MOVEIS LTDA 31.08.2026</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr"/>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1723726</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J321" t="b">
+        <v>0</v>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" t="n">
+        <v>0</v>
+      </c>
+      <c r="P321" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>1723726 01.20264009577505 - PAULO PERES DOS SANTOS 31.08.2026</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr"/>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1727882</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J322" t="b">
+        <v>0</v>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
+      <c r="P322" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>1727882 01.20263700816786 - AILTON DINIZ BUCELLI 31.08.2026</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1730707</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J323" t="b">
+        <v>0</v>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
+      <c r="P323" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>1730707 01.20264460882057 - MARCOS IVAN APARECIDO CANOVA 31.08.2026</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr"/>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1728818</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>DETUNEIRASDOOESTE APARECIDADOOESTE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J324" t="b">
+        <v>0</v>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
+      <c r="P324" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>1728818 01.20264376679609 - MUNICIPIO DE TUNEIRAS DO OESTE 03.09.2026</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr"/>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1734449</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J325" t="b">
+        <v>0</v>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0</v>
+      </c>
+      <c r="P325" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>1734449 01.20264824094562 - VGM EMPREENDIMENTOS IMOBILIARIOS LTDA 31.08.2026</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr"/>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1731945</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>086008</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>673,313</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>673.313</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>R$46.847,53</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J326" t="b">
+        <v>0</v>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0</v>
+      </c>
+      <c r="P326" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>AES 86008 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>1731945 01.20264669355275 - RONALDO DE OLIVEIRA 31.08.2026</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>⚠ AE '086008' em múltiplos projetos: 1722905, 1723726, 1727882, 1730707, 1728818, 1734449, 1731945</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr"/>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86008 4600026463 HAGAP.pdf', 'ae': '086008'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1671216</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CIANORTE</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>99,930</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J327" t="b">
+        <v>0</v>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>1671216 - relocação ra 51028</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr"/>
+      <c r="U327" t="inlineStr"/>
+      <c r="V327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1683425</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="n">
+        <v>0</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>R$ 8.481,96</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J328" t="b">
+        <v>0</v>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" t="n">
+        <v>0</v>
+      </c>
+      <c r="P328" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>1683425 01.20264153503686 - SECRETARIA DE ESTADO DA SEGURANCA PUBLICA 28.10.2026</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr"/>
+      <c r="U328" t="inlineStr"/>
+      <c r="V328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1701624</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Q J</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J329" t="b">
+        <v>0</v>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" t="n">
+        <v>0</v>
+      </c>
+      <c r="P329" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q329" t="inlineStr"/>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>1701624-UC 76602451_CTO 8940809636_SS 20252289230881</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr"/>
+      <c r="U329" t="inlineStr"/>
+      <c r="V329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1718689</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>TERRABOA</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J330" t="b">
+        <v>0</v>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0</v>
+      </c>
+      <c r="P330" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>1718689 UC 17425441_CTO 8940810213_SS20263657660244</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr"/>
+      <c r="U330" t="inlineStr"/>
+      <c r="V330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1718953</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>02.05.2027</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>R$ 89.094,20</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J331" t="b">
+        <v>0</v>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
+      <c r="P331" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q331" t="inlineStr"/>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>1718953 01.20264175521075 - MUNICIPIO DE DOURADINA 23.10.2026</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr"/>
+      <c r="U331" t="inlineStr"/>
+      <c r="V331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>1721631</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="n">
+        <v>0</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J332" t="b">
+        <v>0</v>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="P332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>1721631 UC 113241445_CTO 8940841901_SS 20263737097721</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr"/>
+      <c r="U332" t="inlineStr"/>
+      <c r="V332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>1729927</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>TUNEIRASDOOESTE</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="n">
+        <v>0</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J333" t="b">
+        <v>0</v>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="P333" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q333" t="inlineStr"/>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>1729927 - ALNU392492026 - TAPEJARA</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr"/>
+      <c r="U333" t="inlineStr"/>
+      <c r="V333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1730822</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>15.06.2027</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J334" t="b">
+        <v>0</v>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="P334" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q334" t="inlineStr"/>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>1730822 01.20264461840418 - MARCOS ANTONIO BRONZI 28.10.2026</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr"/>
+      <c r="U334" t="inlineStr"/>
+      <c r="V334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>1733419</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>MARIAHELENA</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J335" t="b">
+        <v>0</v>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="P335" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>1733419 UC 51300257_CTO 8940835589_SS 20264760202819</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr"/>
+      <c r="U335" t="inlineStr"/>
+      <c r="V335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>1715154I</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="n">
+        <v>0</v>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J336" t="b">
+        <v>1</v>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="N336" t="n">
+        <v>1</v>
+      </c>
+      <c r="O336" t="n">
+        <v>1</v>
+      </c>
+      <c r="P336" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr"/>
+      <c r="U336" t="inlineStr"/>
+      <c r="V336" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V336"/>
+  <dimension ref="A1:V342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,11 +927,15 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -947,7 +951,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1429,20 +1433,28 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1455,7 +1467,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -2713,24 +2725,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2971,24 +2991,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
@@ -3323,20 +3351,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
         <v>4</v>
@@ -3353,7 +3389,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3909,11 +3945,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3921,12 +3957,16 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N42" t="n">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3995,20 +4035,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
         <v>6</v>
@@ -4025,7 +4073,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4605,24 +4653,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>02.07.2026</t>
+        </is>
+      </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>5</v>
@@ -4706,10 +4762,14 @@
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -4961,20 +5021,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
         <v>3</v>
@@ -4991,7 +5059,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -5299,7 +5367,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5569,11 +5637,19 @@
       <c r="J61" t="b">
         <v>0</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -5589,7 +5665,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5645,20 +5721,28 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
         <v>4</v>
@@ -5675,7 +5759,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -7063,20 +7147,28 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" t="n">
         <v>1</v>
@@ -7089,7 +7181,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8821,24 +8913,32 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -9191,24 +9291,32 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -9415,24 +9523,32 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" t="n">
         <v>6</v>
@@ -11109,7 +11225,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11251,11 +11367,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11263,12 +11379,16 @@
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
       <c r="N155" t="n">
         <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P155" t="n">
         <v>6</v>
@@ -12177,7 +12297,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12267,7 +12387,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12353,7 +12473,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12439,7 +12559,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12529,7 +12649,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -12615,7 +12735,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13041,7 +13161,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13131,7 +13251,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13217,7 +13337,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13303,7 +13423,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13389,7 +13509,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13471,7 +13591,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -13775,24 +13895,32 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P191" t="n">
         <v>0</v>
@@ -16939,11 +17067,15 @@
       <c r="J232" t="b">
         <v>0</v>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -16963,7 +17095,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -17021,11 +17153,15 @@
       <c r="J233" t="b">
         <v>0</v>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -17045,7 +17181,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -17103,11 +17239,15 @@
       <c r="J234" t="b">
         <v>0</v>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -17127,7 +17267,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -17185,11 +17325,15 @@
       <c r="J235" t="b">
         <v>0</v>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -17209,7 +17353,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -17507,11 +17651,15 @@
       <c r="J240" t="b">
         <v>0</v>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -17531,7 +17679,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -18359,24 +18507,32 @@
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P251" t="n">
         <v>0</v>
@@ -18527,7 +18683,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18601,7 +18757,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -18679,7 +18835,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -19563,24 +19719,32 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
       <c r="N269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P269" t="n">
         <v>0</v>
@@ -19667,24 +19831,32 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
       <c r="N271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P271" t="n">
         <v>0</v>
@@ -19733,24 +19905,32 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
       <c r="N272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P272" t="n">
         <v>12</v>
@@ -19787,24 +19967,32 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J273" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
       <c r="N273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P273" t="n">
         <v>0</v>
@@ -19837,24 +20025,32 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
       <c r="N274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P274" t="n">
         <v>0</v>
@@ -20048,10 +20244,14 @@
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -23946,15 +24146,23 @@
           <t>1683425</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>086019</t>
+        </is>
+      </c>
       <c r="C328" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>1.033,676</t>
+        </is>
+      </c>
       <c r="E328" t="n">
-        <v>0</v>
+        <v>1033.676</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -23991,7 +24199,11 @@
       <c r="P328" t="n">
         <v>5</v>
       </c>
-      <c r="Q328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>AES 86019 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R328" t="inlineStr">
         <is>
           <t>1683425 01.20264153503686 - SECRETARIA DE ESTADO DA SEGURANCA PUBLICA 28.10.2026</t>
@@ -23999,12 +24211,20 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T328" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>⚠ AE '086019' em múltiplos projetos: 1683425, 1718953, 1730822</t>
+        </is>
+      </c>
       <c r="U328" t="inlineStr"/>
-      <c r="V328" t="inlineStr"/>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86019 4600026463 HAGAP.pdf', 'ae': '086019'}]</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -24136,15 +24356,23 @@
           <t>1718953</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>086019</t>
+        </is>
+      </c>
       <c r="C331" t="inlineStr">
         <is>
           <t>DEDOURADINA</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>1.033,676</t>
+        </is>
+      </c>
       <c r="E331" t="n">
-        <v>0</v>
+        <v>1033.676</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -24181,7 +24409,11 @@
       <c r="P331" t="n">
         <v>5</v>
       </c>
-      <c r="Q331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>AES 86019 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R331" t="inlineStr">
         <is>
           <t>1718953 01.20264175521075 - MUNICIPIO DE DOURADINA 23.10.2026</t>
@@ -24189,12 +24421,20 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T331" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>⚠ AE '086019' em múltiplos projetos: 1683425, 1718953, 1730822</t>
+        </is>
+      </c>
       <c r="U331" t="inlineStr"/>
-      <c r="V331" t="inlineStr"/>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86019 4600026463 HAGAP.pdf', 'ae': '086019'}]</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -24326,15 +24566,23 @@
           <t>1730822</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>086019</t>
+        </is>
+      </c>
       <c r="C334" t="inlineStr">
         <is>
           <t>AZEVEDO</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1.033,676</t>
+        </is>
+      </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>1033.676</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -24346,7 +24594,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>R$68.930,71</t>
+        </is>
+      </c>
       <c r="I334" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -24367,7 +24619,11 @@
       <c r="P334" t="n">
         <v>3</v>
       </c>
-      <c r="Q334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>AES 86019 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R334" t="inlineStr">
         <is>
           <t>1730822 01.20264461840418 - MARCOS ANTONIO BRONZI 28.10.2026</t>
@@ -24375,12 +24631,20 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T334" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>⚠ AE '086019' em múltiplos projetos: 1683425, 1718953, 1730822</t>
+        </is>
+      </c>
       <c r="U334" t="inlineStr"/>
-      <c r="V334" t="inlineStr"/>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86019 4600026463 HAGAP.pdf', 'ae': '086019'}]</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -24498,6 +24762,350 @@
       <c r="U336" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1663544</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J337" t="b">
+        <v>1</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>1</v>
+      </c>
+      <c r="O337" t="n">
+        <v>1</v>
+      </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr"/>
+      <c r="U337" t="inlineStr"/>
+      <c r="V337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1682195</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J338" t="b">
+        <v>1</v>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="N338" t="n">
+        <v>1</v>
+      </c>
+      <c r="O338" t="n">
+        <v>1</v>
+      </c>
+      <c r="P338" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr"/>
+      <c r="U338" t="inlineStr"/>
+      <c r="V338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>1693027</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J339" t="b">
+        <v>1</v>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="N339" t="n">
+        <v>1</v>
+      </c>
+      <c r="O339" t="n">
+        <v>1</v>
+      </c>
+      <c r="P339" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q339" t="inlineStr"/>
+      <c r="R339" t="inlineStr"/>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr"/>
+      <c r="U339" t="inlineStr"/>
+      <c r="V339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1713660I</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J340" t="b">
+        <v>1</v>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="N340" t="n">
+        <v>1</v>
+      </c>
+      <c r="O340" t="n">
+        <v>1</v>
+      </c>
+      <c r="P340" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q340" t="inlineStr"/>
+      <c r="R340" t="inlineStr"/>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr"/>
+      <c r="U340" t="inlineStr"/>
+      <c r="V340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1671216I</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>086018</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>145,584</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>145.584</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>R$8.880,62</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J341" t="b">
+        <v>0</v>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="n">
+        <v>0</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0</v>
+      </c>
+      <c r="P341" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>AES 86018 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr"/>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr"/>
+      <c r="U341" t="inlineStr"/>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86018 4600026463 HAGAP.pdf', 'ae': '086018'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>1702640I</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J342" t="b">
+        <v>1</v>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="N342" t="n">
+        <v>1</v>
+      </c>
+      <c r="O342" t="n">
+        <v>1</v>
+      </c>
+      <c r="P342" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q342" t="inlineStr"/>
+      <c r="R342" t="inlineStr"/>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr"/>
+      <c r="U342" t="inlineStr"/>
+      <c r="V342" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V342"/>
+  <dimension ref="A1:V360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,24 +569,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>16.07.2026</t>
+        </is>
+      </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -1525,11 +1533,15 @@
       <c r="J13" t="b">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1545,7 +1557,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2307,24 +2319,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>6</v>
@@ -2637,7 +2657,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4379,24 +4399,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
         <v>3</v>
@@ -4751,11 +4779,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4767,12 +4795,16 @@
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N51" t="n">
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
         <v>4</v>
@@ -4845,20 +4877,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4875,7 +4915,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -4931,24 +4971,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" t="n">
         <v>3</v>
@@ -6165,11 +6213,15 @@
       <c r="J67" t="b">
         <v>0</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -6189,7 +6241,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -9867,24 +9919,32 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -11965,20 +12025,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J166" t="b">
-        <v>0</v>
-      </c>
-      <c r="K166" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -11991,7 +12059,7 @@
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -12483,20 +12551,28 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J173" t="b">
-        <v>0</v>
-      </c>
-      <c r="K173" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P173" t="n">
         <v>6</v>
@@ -12513,7 +12589,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
@@ -12665,11 +12741,15 @@
       <c r="J175" t="b">
         <v>0</v>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -12689,7 +12769,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
@@ -12827,24 +12907,32 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P177" t="n">
         <v>0</v>
@@ -13171,24 +13259,32 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P181" t="n">
         <v>3</v>
@@ -13353,11 +13449,15 @@
       <c r="J183" t="b">
         <v>0</v>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -13377,7 +13477,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -13439,11 +13539,15 @@
       <c r="J184" t="b">
         <v>0</v>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -13463,7 +13567,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -14229,11 +14333,15 @@
       <c r="J195" t="b">
         <v>0</v>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -14253,7 +14361,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -15145,24 +15253,32 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P206" t="n">
         <v>4</v>
@@ -15423,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="P209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -15589,11 +15705,15 @@
       <c r="J211" t="b">
         <v>0</v>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -15613,7 +15733,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
@@ -16460,15 +16580,23 @@
           <t>1722805</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>085243</t>
+        </is>
+      </c>
       <c r="C225" t="inlineStr">
         <is>
           <t>DEASCHORK AZEVEDO</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>327,110</t>
+        </is>
+      </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>327.11</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -16505,7 +16633,11 @@
       <c r="P225" t="n">
         <v>3</v>
       </c>
-      <c r="Q225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>AES 85243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R225" t="inlineStr">
         <is>
           <t>1722805 01.20263889838038 - EPR PARANA S.A 16.09</t>
@@ -16513,12 +16645,20 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T225" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>⚠ AE '085243' em múltiplos projetos: 1722805, 1727881S</t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr"/>
-      <c r="V225" t="inlineStr"/>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85243 4600026463 HAGAP.pdf', 'ae': '085243'}]</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -17737,11 +17877,15 @@
       <c r="J241" t="b">
         <v>0</v>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -17761,7 +17905,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -17989,20 +18133,32 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J244" t="b">
-        <v>0</v>
-      </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>MULTA-1726890-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P244" t="n">
         <v>5</v>
@@ -18019,7 +18175,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
@@ -18075,20 +18231,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J245" t="b">
-        <v>0</v>
-      </c>
-      <c r="K245" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P245" t="n">
         <v>6</v>
@@ -18105,7 +18269,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
@@ -19103,7 +19267,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -19113,20 +19277,28 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J260" t="b">
-        <v>0</v>
-      </c>
-      <c r="K260" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P260" t="n">
         <v>5</v>
@@ -19143,7 +19315,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
@@ -19361,7 +19533,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20287,24 +20459,32 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P279" t="n">
         <v>0</v>
@@ -20337,24 +20517,32 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P280" t="n">
         <v>0</v>
@@ -20507,20 +20695,28 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J283" t="b">
-        <v>0</v>
-      </c>
-      <c r="K283" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P283" t="n">
         <v>0</v>
@@ -20533,7 +20729,7 @@
       <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -20917,7 +21113,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21003,7 +21199,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -21019,11 +21215,15 @@
       <c r="J290" t="b">
         <v>0</v>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -21043,7 +21243,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T290" t="inlineStr">
@@ -21089,7 +21289,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -21175,7 +21375,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -21261,7 +21461,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -21347,7 +21547,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -21433,7 +21633,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -21449,11 +21649,15 @@
       <c r="J295" t="b">
         <v>0</v>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -21473,7 +21677,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -21519,7 +21723,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -21921,7 +22125,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -22007,7 +22211,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -22093,7 +22297,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22179,7 +22383,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22367,11 +22571,15 @@
       <c r="J306" t="b">
         <v>0</v>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O306" t="n">
         <v>0</v>
@@ -22391,7 +22599,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T306" t="inlineStr">
@@ -23709,7 +23917,7 @@
         <v>0</v>
       </c>
       <c r="P322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -25106,6 +25314,1334 @@
       <c r="U342" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>1727881S</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>085243</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>327,110</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>R$23.692,57</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J343" t="b">
+        <v>0</v>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" t="n">
+        <v>0</v>
+      </c>
+      <c r="P343" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>AES 85243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr"/>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>⚠ AE '085243' em múltiplos projetos: 1722805, 1727881S</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr"/>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 85243 4600026463 HAGAP.pdf', 'ae': '085243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1734372</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>086178</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>RDS UMUARAMA</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>177,193</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>177.193</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>R$10.808,77</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J344" t="b">
+        <v>0</v>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="n">
+        <v>0</v>
+      </c>
+      <c r="O344" t="n">
+        <v>0</v>
+      </c>
+      <c r="P344" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>AES 86178 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>1734372 Essenza Subterrânea</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr"/>
+      <c r="U344" t="inlineStr"/>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86178 4600026463 HAGAP.pdf', 'ae': '086178'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1570218</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>086179</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>TAPEJARA</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2.427,208</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>2427.208</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>R$185.341,60</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J345" t="b">
+        <v>0</v>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="n">
+        <v>0</v>
+      </c>
+      <c r="O345" t="n">
+        <v>0</v>
+      </c>
+      <c r="P345" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>AES 86179 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>1570218</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr"/>
+      <c r="U345" t="inlineStr"/>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86179 4600026463 HAGAP.pdf', 'ae': '086179'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>1570304</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>086180</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>TAPEJARA</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>1.330,850</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>1330.85</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>R$101.623,70</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J346" t="b">
+        <v>0</v>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="n">
+        <v>0</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
+      <c r="P346" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>AES 86180 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>1570304</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr"/>
+      <c r="U346" t="inlineStr"/>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86180 4600026463 HAGAP.pdf', 'ae': '086180'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1570303</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>086181</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>WESLEY ORTIZ DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2.397,654</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>2397.654</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>R$183.084,85</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J347" t="b">
+        <v>0</v>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
+      <c r="P347" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>AES 86181 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>1570303</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr"/>
+      <c r="U347" t="inlineStr"/>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86181 4600026463 HAGAP.pdf', 'ae': '086181'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1570221</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>086182</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>TAPEJARA</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>1.623,353</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>1623.353</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>R$123.959,23</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J348" t="b">
+        <v>0</v>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="n">
+        <v>0</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0</v>
+      </c>
+      <c r="P348" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>AES 86182 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>1570221</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr"/>
+      <c r="U348" t="inlineStr"/>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86182 4600026463 HAGAP.pdf', 'ae': '086182'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1570220</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>086183</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>TAPERAJA</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2.993,244</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>2993.244</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>R$228.564,09</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J349" t="b">
+        <v>0</v>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
+      <c r="P349" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>AES 86183 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>1570220 -(1733119)</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>⚠ AE '086183' em múltiplos projetos: 1570220, 1636670, 1570222, 1719992</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr"/>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86183 4600026463 HAGAP.pdf', 'ae': '086183'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1636670</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>086183</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2.993,244</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>2993.244</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>R$228.564,09</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J350" t="b">
+        <v>0</v>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>AES 86183 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>1636670 - R.A TAPEJARA LDNU335782024 - SEM VIA PROJETO</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>⚠ AE '086183' em múltiplos projetos: 1570220, 1636670, 1570222, 1719992</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr"/>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86183 4600026463 HAGAP.pdf', 'ae': '086183'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1570222</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>086183</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>TAPEJARA</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2.993,244</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>2993.244</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>R$228.564,09</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J351" t="b">
+        <v>0</v>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
+      <c r="P351" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>AES 86183 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>1570222</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>⚠ AE '086183' em múltiplos projetos: 1570220, 1636670, 1570222, 1719992</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr"/>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86183 4600026463 HAGAP.pdf', 'ae': '086183'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>1719992</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>086183</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2.993,244</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>2993.244</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>R$228.564,09</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J352" t="b">
+        <v>0</v>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="n">
+        <v>0</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0</v>
+      </c>
+      <c r="P352" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>AES 86183 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>1719992 - BRT TAPEJARA LDNU335782024 - SEM VIA PROJETO</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>⚠ AE '086183' em múltiplos projetos: 1570220, 1636670, 1570222, 1719992</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr"/>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86183 4600026463 HAGAP.pdf', 'ae': '086183'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>1733119</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>086184</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>1.425,015</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>1425.015</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>R$108.814,14</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J353" t="b">
+        <v>0</v>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="n">
+        <v>0</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+      <c r="P353" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>AES 86184 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr"/>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr"/>
+      <c r="U353" t="inlineStr"/>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86184 4600026463 HAGAP.pdf', 'ae': '086184'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>1734835I</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>086185</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>283,497</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>283.497</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>R$17.293,31</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J354" t="b">
+        <v>0</v>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="n">
+        <v>0</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0</v>
+      </c>
+      <c r="P354" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>AES 86185 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr"/>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr"/>
+      <c r="U354" t="inlineStr"/>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86185 4600026463 HAGAP.pdf', 'ae': '086185'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>1722924</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>086186</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>257,242</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>257.242</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>R$19.642,99</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J355" t="b">
+        <v>0</v>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" t="n">
+        <v>0</v>
+      </c>
+      <c r="P355" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>AES 86186 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>1722924 01.20263943597790 - JOSE ROBERTO MATIAS 21.10.2026</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr"/>
+      <c r="U355" t="inlineStr"/>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86186 4600026463 HAGAP.pdf', 'ae': '086186'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>1734835</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J356" t="b">
+        <v>0</v>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="n">
+        <v>0</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0</v>
+      </c>
+      <c r="P356" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>1734835 UC 80541267_CTO 8940822119_ SS 202648514241158</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr"/>
+      <c r="U356" t="inlineStr"/>
+      <c r="V356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1707174</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J357" t="b">
+        <v>1</v>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>1</v>
+      </c>
+      <c r="O357" t="n">
+        <v>1</v>
+      </c>
+      <c r="P357" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr"/>
+      <c r="U357" t="inlineStr"/>
+      <c r="V357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1713351</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="n">
+        <v>0</v>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J358" t="b">
+        <v>1</v>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>1</v>
+      </c>
+      <c r="O358" t="n">
+        <v>1</v>
+      </c>
+      <c r="P358" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr"/>
+      <c r="U358" t="inlineStr"/>
+      <c r="V358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>1712963I</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J359" t="b">
+        <v>0</v>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="n">
+        <v>1</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+      <c r="P359" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr"/>
+      <c r="U359" t="inlineStr"/>
+      <c r="V359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>1715710</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J360" t="b">
+        <v>1</v>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>1</v>
+      </c>
+      <c r="O360" t="n">
+        <v>1</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr"/>
+      <c r="U360" t="inlineStr"/>
+      <c r="V360" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -5939,7 +5939,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6479,11 +6479,15 @@
       <c r="J70" t="b">
         <v>0</v>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -6503,7 +6507,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -6545,7 +6549,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6635,7 +6639,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6725,7 +6729,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7415,11 +7419,15 @@
       <c r="J84" t="b">
         <v>0</v>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -7439,7 +7447,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -11539,24 +11547,32 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -12015,7 +12031,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12101,7 +12117,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12315,7 +12331,7 @@
       </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -13249,7 +13265,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13347,7 +13363,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13433,7 +13449,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13523,7 +13539,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13613,7 +13629,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13695,7 +13711,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14849,11 +14865,15 @@
       <c r="J201" t="b">
         <v>0</v>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -14873,7 +14893,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
@@ -15357,11 +15377,15 @@
       <c r="J207" t="b">
         <v>0</v>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -15381,7 +15405,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
@@ -15881,11 +15905,15 @@
       <c r="J213" t="b">
         <v>0</v>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -15905,7 +15933,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
@@ -16033,7 +16061,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -18331,11 +18359,15 @@
       <c r="J246" t="b">
         <v>0</v>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -18355,7 +18387,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
@@ -21805,7 +21837,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -21883,7 +21915,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -21961,7 +21993,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -22043,7 +22075,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -22813,7 +22845,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -22899,7 +22931,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -22985,7 +23017,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -23071,7 +23103,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -25341,7 +25373,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V360"/>
+  <dimension ref="A1:V363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,7 +559,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2673,11 +2673,15 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2697,7 +2701,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -4245,11 +4249,15 @@
       <c r="J45" t="b">
         <v>0</v>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -4265,7 +4273,7 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -5955,11 +5963,15 @@
       <c r="J64" t="b">
         <v>0</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -5979,7 +5991,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8155,24 +8167,32 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -11293,7 +11313,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11913,24 +11933,32 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P164" t="n">
         <v>0</v>
@@ -13727,11 +13755,15 @@
       <c r="J186" t="b">
         <v>0</v>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -13747,7 +13779,7 @@
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
@@ -14525,11 +14557,15 @@
       <c r="J197" t="b">
         <v>0</v>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -14549,7 +14585,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -15467,11 +15503,15 @@
       <c r="J208" t="b">
         <v>0</v>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -15491,7 +15531,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
@@ -15633,24 +15673,32 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
       <c r="N210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P210" t="n">
         <v>4</v>
@@ -16517,11 +16565,15 @@
       <c r="J223" t="b">
         <v>0</v>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -16537,7 +16589,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -16821,11 +16873,15 @@
       <c r="J227" t="b">
         <v>0</v>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -16845,7 +16901,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
@@ -16907,11 +16963,15 @@
       <c r="J228" t="b">
         <v>0</v>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -16931,7 +16991,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -16989,11 +17049,15 @@
       <c r="J229" t="b">
         <v>0</v>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -17013,7 +17077,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -17071,11 +17135,15 @@
       <c r="J230" t="b">
         <v>0</v>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -17095,7 +17163,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -18591,20 +18659,28 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J249" t="b">
-        <v>0</v>
-      </c>
-      <c r="K249" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>21.07.2026</t>
+        </is>
+      </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P249" t="n">
         <v>4</v>
@@ -18621,7 +18697,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -19235,20 +19311,28 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J259" t="b">
-        <v>0</v>
-      </c>
-      <c r="K259" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P259" t="n">
         <v>2</v>
@@ -19261,7 +19345,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -19409,11 +19493,15 @@
       <c r="J261" t="b">
         <v>0</v>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -19433,7 +19521,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -19575,20 +19663,28 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J263" t="b">
-        <v>0</v>
-      </c>
-      <c r="K263" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P263" t="n">
         <v>4</v>
@@ -19605,7 +19701,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
@@ -22763,7 +22859,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -22779,11 +22875,15 @@
       <c r="J308" t="b">
         <v>0</v>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O308" t="n">
         <v>0</v>
@@ -22803,7 +22903,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T308" t="inlineStr"/>
@@ -22947,11 +23047,15 @@
       <c r="J310" t="b">
         <v>0</v>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -22971,7 +23075,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T310" t="inlineStr">
@@ -23291,11 +23395,15 @@
       <c r="J314" t="b">
         <v>0</v>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -23315,7 +23423,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T314" t="inlineStr">
@@ -23443,7 +23551,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -23517,7 +23625,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -26674,6 +26782,168 @@
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>1707182</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="n">
+        <v>0</v>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J361" t="b">
+        <v>0</v>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="n">
+        <v>1</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr"/>
+      <c r="U361" t="inlineStr"/>
+      <c r="V361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1713903C</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J362" t="b">
+        <v>1</v>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>1</v>
+      </c>
+      <c r="O362" t="n">
+        <v>1</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr"/>
+      <c r="U362" t="inlineStr"/>
+      <c r="V362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1713903I</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="n">
+        <v>0</v>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J363" t="b">
+        <v>1</v>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>MULTA-1713903I-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>2</v>
+      </c>
+      <c r="O363" t="n">
+        <v>1</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q363" t="inlineStr"/>
+      <c r="R363" t="inlineStr"/>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr"/>
+      <c r="U363" t="inlineStr"/>
+      <c r="V363" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V363"/>
+  <dimension ref="A1:V381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,7 +559,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2003,20 +2003,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2029,7 +2037,7 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2071,7 +2079,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2149,7 +2157,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2159,20 +2167,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2185,7 +2201,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2227,7 +2243,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2739,7 +2755,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2829,7 +2845,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2839,24 +2855,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -2915,7 +2939,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2925,24 +2949,32 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>5</v>
@@ -3005,7 +3037,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3103,7 +3135,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3189,7 +3221,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3199,20 +3231,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>5</v>
@@ -3229,7 +3269,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3275,7 +3315,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3881,7 +3921,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3959,7 +3999,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4049,7 +4089,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4143,7 +4183,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4233,7 +4273,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4315,7 +4355,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5265,24 +5305,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -5347,24 +5395,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -5519,20 +5575,32 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>MULTA - 1719775 - HAGAP - 27-07-2026.pdf</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
         <v>4</v>
@@ -5549,7 +5617,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -6047,20 +6115,28 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
         <v>4</v>
@@ -6077,7 +6153,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -6309,24 +6385,32 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
         <v>4</v>
@@ -6571,24 +6655,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
         <v>3</v>
@@ -6661,24 +6753,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>4</v>
@@ -7425,24 +7525,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84" t="n">
         <v>6</v>
@@ -8020,10 +8128,14 @@
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -8677,24 +8789,32 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" t="n">
         <v>4</v>
@@ -8731,24 +8851,32 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -9781,24 +9909,32 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -11883,24 +12019,32 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -12059,7 +12203,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12145,7 +12289,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12941,7 +13085,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13035,7 +13179,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13121,7 +13265,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13207,7 +13351,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14455,7 +14599,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14465,20 +14609,28 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J196" t="b">
-        <v>0</v>
-      </c>
-      <c r="K196" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" t="n">
         <v>3</v>
@@ -14495,7 +14647,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -14551,24 +14703,32 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P197" t="n">
         <v>3</v>
@@ -14647,11 +14807,15 @@
       <c r="J198" t="b">
         <v>0</v>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -14671,7 +14835,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -15947,24 +16111,32 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P213" t="n">
         <v>3</v>
@@ -16109,7 +16281,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16119,20 +16291,28 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J215" t="b">
-        <v>0</v>
-      </c>
-      <c r="K215" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P215" t="n">
         <v>3</v>
@@ -16149,7 +16329,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -17480,10 +17660,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -17892,10 +18076,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -18965,20 +19153,28 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J254" t="b">
-        <v>0</v>
-      </c>
-      <c r="K254" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P254" t="n">
         <v>0</v>
@@ -18991,7 +19187,7 @@
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -19045,11 +19241,15 @@
       <c r="J255" t="b">
         <v>0</v>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -19065,7 +19265,7 @@
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
@@ -19123,11 +19323,15 @@
       <c r="J256" t="b">
         <v>0</v>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -19143,7 +19347,7 @@
       <c r="R256" t="inlineStr"/>
       <c r="S256" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
@@ -19185,7 +19389,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -19577,20 +19781,32 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J262" t="b">
-        <v>0</v>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>MULTA-1727529-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P262" t="n">
         <v>3</v>
@@ -19607,7 +19823,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
@@ -20813,7 +21029,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -20899,7 +21115,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20977,7 +21193,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -21177,24 +21393,32 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -21337,24 +21561,32 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P290" t="n">
         <v>4</v>
@@ -22021,20 +22253,28 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J298" t="b">
-        <v>0</v>
-      </c>
-      <c r="K298" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P298" t="n">
         <v>0</v>
@@ -22047,7 +22287,7 @@
       <c r="R298" t="inlineStr"/>
       <c r="S298" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
@@ -22171,7 +22411,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -22521,20 +22761,28 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J304" t="b">
-        <v>0</v>
-      </c>
-      <c r="K304" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P304" t="n">
         <v>4</v>
@@ -22551,7 +22799,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T304" t="inlineStr">
@@ -22597,7 +22845,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -22683,7 +22931,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -22773,7 +23021,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -22859,7 +23107,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -23041,24 +23289,32 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J310" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr"/>
-      <c r="M310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P310" t="n">
         <v>6</v>
@@ -23131,20 +23387,28 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J311" t="b">
-        <v>0</v>
-      </c>
-      <c r="K311" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
       <c r="N311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P311" t="n">
         <v>5</v>
@@ -23161,7 +23425,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T311" t="inlineStr">
@@ -23859,7 +24123,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -23945,7 +24209,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -24031,7 +24295,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24117,7 +24381,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -24203,7 +24467,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -24289,7 +24553,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -24375,7 +24639,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -24955,11 +25219,15 @@
       <c r="J334" t="b">
         <v>0</v>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr"/>
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O334" t="n">
         <v>0</v>
@@ -24979,7 +25247,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T334" t="inlineStr">
@@ -25481,7 +25749,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -25563,7 +25831,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -26944,6 +27212,1394 @@
       <c r="U363" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1720908</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>DETERRABOA CENTRO</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J364" t="b">
+        <v>0</v>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>1720908 01.20263825958330 - MUNICIPIO DE TERRA BOA 21-09-2026</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr"/>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1725529</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>DEALTONIA RURAL</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J365" t="b">
+        <v>0</v>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
+      <c r="P365" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>1725529 01.20264126275408 - MUNICIPIO DE ALTONIA 21-09-2026</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr"/>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1730751</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J366" t="b">
+        <v>0</v>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
+      <c r="P366" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>1730751 01.20264498209022 - PAULO EDUARDO MORETI RIBEIRO 21-09-2026</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr"/>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1733600</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J367" t="b">
+        <v>0</v>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
+      <c r="P367" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>1733600 01.20264718735547 - DOUGLAS MACIEL DA SILVA MARTINS 21-09-2026</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr"/>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>1733602</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J368" t="b">
+        <v>0</v>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
+      <c r="P368" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>1733602 01.20264749353720 - MARILENE FLAUSINA DA SILVA - FALTA PROJETO EDUARDO LISBOA 18-08-2026</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr"/>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>1734089</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J369" t="b">
+        <v>0</v>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="n">
+        <v>0</v>
+      </c>
+      <c r="O369" t="n">
+        <v>0</v>
+      </c>
+      <c r="P369" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>1734089 01.20264759270356 - THIAGO POSSAGNO ULIANA 18-09-2026</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr"/>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>1734974</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>086631</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>517,979</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>517.979</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>R$34.510,68</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J370" t="b">
+        <v>0</v>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="n">
+        <v>0</v>
+      </c>
+      <c r="O370" t="n">
+        <v>0</v>
+      </c>
+      <c r="P370" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>AES 86631 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>1734974 01.20264798519967 - JOSE DANCIGER DE MAGALHAES - FALTA PROJETO EDUARDO LISBOA 21-09-2026</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>⚠ AE '086631' em múltiplos projetos: 1720908, 1725529, 1730751, 1733600, 1733602, 1734089, 1734974</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr"/>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86631 4600026463 HAGAP.pdf', 'ae': '086631'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1728057</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>086632</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>1.496,245</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>1496.245</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>R$97.866,42</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J371" t="b">
+        <v>0</v>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="n">
+        <v>0</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0</v>
+      </c>
+      <c r="P371" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>AES 86632 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>1728057 01.20264292380753 - PAULO ROBERTO ZANCAN 11-11-2026</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>⚠ AE '086632' em múltiplos projetos: 1728057, 1729801, 1730867, 1731940, 1733160, 1734965</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr"/>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86632 4600026463 HAGAP.pdf', 'ae': '086632'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1729801</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>086632</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>1.496,245</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>1496.245</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>R$97.866,42</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J372" t="b">
+        <v>0</v>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="n">
+        <v>0</v>
+      </c>
+      <c r="O372" t="n">
+        <v>0</v>
+      </c>
+      <c r="P372" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>AES 86632 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>1729801 01.20264455155545 - AMILTOM PEREZ 23-11-2026</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>⚠ AE '086632' em múltiplos projetos: 1728057, 1729801, 1730867, 1731940, 1733160, 1734965</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr"/>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86632 4600026463 HAGAP.pdf', 'ae': '086632'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>1730867</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>086632</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>1.496,245</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>1496.245</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>R$97.866,42</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J373" t="b">
+        <v>0</v>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
+      <c r="P373" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>AES 86632 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>1730867 01.20264548669722 - MARIA APARECIDA CASSAVARA JUSTINO 03-11-2026</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>⚠ AE '086632' em múltiplos projetos: 1728057, 1729801, 1730867, 1731940, 1733160, 1734965</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86632 4600026463 HAGAP.pdf', 'ae': '086632'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1731940</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>086632</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>CANTELLI AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>1.496,245</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>1496.245</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>R$97.866,42</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J374" t="b">
+        <v>0</v>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
+      <c r="P374" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>AES 86632 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>1731940 01.20264644189952 - MIKAI SORVETES E ACAI LTDA 12-11-2026</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>⚠ AE '086632' em múltiplos projetos: 1728057, 1729801, 1730867, 1731940, 1733160, 1734965</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr"/>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86632 4600026463 HAGAP.pdf', 'ae': '086632'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1733160</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>086632</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>1.496,245</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>1496.245</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>R$97.866,42</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J375" t="b">
+        <v>0</v>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0</v>
+      </c>
+      <c r="P375" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>AES 86632 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>1733160 01.20264737024246 - DIONATTA LIMA DOS SANTOS 10-11-2026</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>⚠ AE '086632' em múltiplos projetos: 1728057, 1729801, 1730867, 1731940, 1733160, 1734965</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr"/>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86632 4600026463 HAGAP.pdf', 'ae': '086632'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>1734965</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>086632</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>CANTELLI AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>1.496,245</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>1496.245</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>R$97.866,42</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J376" t="b">
+        <v>0</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0</v>
+      </c>
+      <c r="P376" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>AES 86632 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>1734965 01.20264740864788 - COYOTE CAR AUTO CENTER LTDA 12-11-2026</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>⚠ AE '086632' em múltiplos projetos: 1728057, 1729801, 1730867, 1731940, 1733160, 1734965</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr"/>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86632 4600026463 HAGAP.pdf', 'ae': '086632'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1729553</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>MOREIRA AZEVEDO EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="n">
+        <v>0</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>30.12.2026</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J377" t="b">
+        <v>0</v>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0</v>
+      </c>
+      <c r="P377" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q377" t="inlineStr"/>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>1729553 100000048876 - CONJUNTO DE MED TRIFÁSICA - TERRA BOA</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr"/>
+      <c r="U377" t="inlineStr"/>
+      <c r="V377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>1659020</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J378" t="b">
+        <v>0</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="n">
+        <v>1</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q378" t="inlineStr"/>
+      <c r="R378" t="inlineStr"/>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr"/>
+      <c r="U378" t="inlineStr"/>
+      <c r="V378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>1667819</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J379" t="b">
+        <v>1</v>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="N379" t="n">
+        <v>1</v>
+      </c>
+      <c r="O379" t="n">
+        <v>1</v>
+      </c>
+      <c r="P379" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q379" t="inlineStr"/>
+      <c r="R379" t="inlineStr"/>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr"/>
+      <c r="U379" t="inlineStr"/>
+      <c r="V379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1702212</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J380" t="b">
+        <v>0</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="n">
+        <v>1</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0</v>
+      </c>
+      <c r="P380" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q380" t="inlineStr"/>
+      <c r="R380" t="inlineStr"/>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr"/>
+      <c r="U380" t="inlineStr"/>
+      <c r="V380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1711454</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J381" t="b">
+        <v>1</v>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>1</v>
+      </c>
+      <c r="O381" t="n">
+        <v>1</v>
+      </c>
+      <c r="P381" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q381" t="inlineStr"/>
+      <c r="R381" t="inlineStr"/>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr"/>
+      <c r="U381" t="inlineStr"/>
+      <c r="V381" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V381"/>
+  <dimension ref="A1:V393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1769,20 +1769,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1795,7 +1803,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1837,7 +1845,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1847,20 +1855,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1873,7 +1889,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1915,7 +1931,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1993,7 +2009,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2079,7 +2095,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2157,7 +2173,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2243,7 +2259,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2755,7 +2771,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2845,7 +2861,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2939,7 +2955,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3037,7 +3053,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3135,7 +3151,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3221,7 +3237,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3315,7 +3331,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3587,11 +3603,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3599,12 +3615,16 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
@@ -3921,7 +3941,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3999,7 +4019,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4089,7 +4109,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4183,7 +4203,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4273,7 +4293,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4355,7 +4375,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5673,20 +5693,28 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
         <v>4</v>
@@ -5703,7 +5731,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -6483,24 +6511,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
         <v>3</v>
@@ -11459,20 +11495,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J153" t="b">
-        <v>0</v>
-      </c>
-      <c r="K153" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P153" t="n">
         <v>0</v>
@@ -11485,7 +11529,7 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -13189,20 +13233,28 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J178" t="b">
-        <v>0</v>
-      </c>
-      <c r="K178" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P178" t="n">
         <v>5</v>
@@ -13219,7 +13271,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -13893,24 +13945,32 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -14263,7 +14323,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -14345,7 +14405,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -14427,7 +14487,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14599,7 +14659,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14791,7 +14851,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14881,7 +14941,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -14967,7 +15027,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -16739,24 +16799,32 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P223" t="n">
         <v>6</v>
@@ -17574,10 +17642,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -17750,10 +17822,14 @@
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -18609,24 +18685,32 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P246" t="n">
         <v>6</v>
@@ -19389,7 +19473,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -19587,7 +19671,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -19691,24 +19775,32 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P261" t="n">
         <v>4</v>
@@ -19869,7 +19961,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -21029,7 +21121,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -21115,7 +21207,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -21193,7 +21285,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -21475,20 +21567,28 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J289" t="b">
-        <v>0</v>
-      </c>
-      <c r="K289" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P289" t="n">
         <v>4</v>
@@ -21505,7 +21605,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T289" t="inlineStr">
@@ -21745,20 +21845,28 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J292" t="b">
-        <v>0</v>
-      </c>
-      <c r="K292" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P292" t="n">
         <v>5</v>
@@ -21775,7 +21883,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
@@ -22003,24 +22111,32 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P295" t="n">
         <v>4</v>
@@ -22855,20 +22971,28 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J305" t="b">
-        <v>0</v>
-      </c>
-      <c r="K305" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
       <c r="N305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P305" t="n">
         <v>3</v>
@@ -22885,7 +23009,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T305" t="inlineStr">
@@ -23031,20 +23155,28 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J307" t="b">
-        <v>0</v>
-      </c>
-      <c r="K307" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr"/>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P307" t="n">
         <v>3</v>
@@ -23061,7 +23193,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T307" t="inlineStr">
@@ -23557,7 +23689,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23643,7 +23775,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23733,7 +23865,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -23963,7 +24095,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24041,7 +24173,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -28336,15 +28468,23 @@
           <t>1729553</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>086612</t>
+        </is>
+      </c>
       <c r="C377" t="inlineStr">
         <is>
           <t>MOREIRA AZEVEDO EXECUÇÃO</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>171,974</t>
+        </is>
+      </c>
       <c r="E377" t="n">
-        <v>0</v>
+        <v>171.974</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28356,7 +28496,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>R$10.490,41</t>
+        </is>
+      </c>
       <c r="I377" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -28377,7 +28521,11 @@
       <c r="P377" t="n">
         <v>3</v>
       </c>
-      <c r="Q377" t="inlineStr"/>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>AES 86612 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R377" t="inlineStr">
         <is>
           <t>1729553 100000048876 - CONJUNTO DE MED TRIFÁSICA - TERRA BOA</t>
@@ -28385,12 +28533,16 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, ae</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
       <c r="U377" t="inlineStr"/>
-      <c r="V377" t="inlineStr"/>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86612 4600026463 HAGAP.pdf', 'ae': '086612'}]</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -28600,6 +28752,882 @@
       <c r="U381" t="inlineStr"/>
       <c r="V381" t="inlineStr"/>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>1738814I</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>086733</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>33,838</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>33.838</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>R$2.583,86</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J382" t="b">
+        <v>0</v>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="P382" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>AES 86733 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>1738814I UC 92285716_CTO 8940826705_ SS 20265134445470</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr"/>
+      <c r="U382" t="inlineStr"/>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86733 4600026463 HAGAP.pdf', 'ae': '086733'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>1737269</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>086734</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>CAFELANDIA</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>625,919</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>625.919</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>R$45.915,63</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J383" t="b">
+        <v>0</v>
+      </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="P383" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>AES 86734 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>1737269 1737270 1737272 1737274 ALOC 38448-2026 - URGENTE BRTS</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>⚠ AE '086734' em múltiplos projetos: 1737269, 1737270, 1737276, 1737280, 1737281</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr"/>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86734 4600026463 HAGAP.pdf', 'ae': '086734'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1737270</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>086734</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>625,919</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>625.919</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>R$45.915,63</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J384" t="b">
+        <v>0</v>
+      </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="P384" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>AES 86734 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr"/>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>⚠ AE '086734' em múltiplos projetos: 1737269, 1737270, 1737276, 1737280, 1737281</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr"/>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86734 4600026463 HAGAP.pdf', 'ae': '086734'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1737276</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>086734</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>NOVA AURORA</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>625,919</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>625.919</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>R$45.915,63</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J385" t="b">
+        <v>0</v>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+      <c r="P385" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>AES 86734 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>1737276 ALOC 38449-2026 - BRTS URGENTE</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>⚠ AE '086734' em múltiplos projetos: 1737269, 1737270, 1737276, 1737280, 1737281</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr"/>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86734 4600026463 HAGAP.pdf', 'ae': '086734'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>1737280</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>086734</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>NOVA AURORA</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>625,919</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>625.919</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>R$45.915,63</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J386" t="b">
+        <v>0</v>
+      </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="P386" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>AES 86734 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>1737280 1737281 ALOC 38447 - 2026 - BRT´S URGENTES</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>⚠ AE '086734' em múltiplos projetos: 1737269, 1737270, 1737276, 1737280, 1737281</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr"/>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86734 4600026463 HAGAP.pdf', 'ae': '086734'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>1737281</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>086734</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>625,919</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>625.919</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>R$45.915,63</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J387" t="b">
+        <v>0</v>
+      </c>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>AES 86734 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr"/>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>⚠ AE '086734' em múltiplos projetos: 1737269, 1737270, 1737276, 1737280, 1737281</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr"/>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86734 4600026463 HAGAP.pdf', 'ae': '086734'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1737483</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>086735</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>CONSTRUÇÃOSFZCEL</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>331,054</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>331.054</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>R$25.279,27</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J388" t="b">
+        <v>0</v>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0</v>
+      </c>
+      <c r="P388" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>AES 86735 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>1737483 _ ARD 4414-2026 - ALIM. JESUITAS - BRT100A - 100000049313</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>⚠ AE '086735' em múltiplos projetos: 1737483, 1737484</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr"/>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86735 4600026463 HAGAP.pdf', 'ae': '086735'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>1737484</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>086735</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>331,054</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>331.054</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>R$25.279,27</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J389" t="b">
+        <v>0</v>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>AES 86735 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr"/>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>⚠ AE '086735' em múltiplos projetos: 1737483, 1737484</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr"/>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 86735 4600026463 HAGAP.pdf', 'ae': '086735'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1694861</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J390" t="b">
+        <v>1</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>1</v>
+      </c>
+      <c r="O390" t="n">
+        <v>1</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q390" t="inlineStr"/>
+      <c r="R390" t="inlineStr"/>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr"/>
+      <c r="U390" t="inlineStr"/>
+      <c r="V390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1710332</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J391" t="b">
+        <v>1</v>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>1</v>
+      </c>
+      <c r="O391" t="n">
+        <v>1</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q391" t="inlineStr"/>
+      <c r="R391" t="inlineStr"/>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr"/>
+      <c r="U391" t="inlineStr"/>
+      <c r="V391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1710287C</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J392" t="b">
+        <v>1</v>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>03.08.2026</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>1</v>
+      </c>
+      <c r="O392" t="n">
+        <v>1</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q392" t="inlineStr"/>
+      <c r="R392" t="inlineStr"/>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr"/>
+      <c r="U392" t="inlineStr"/>
+      <c r="V392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1692415</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J393" t="b">
+        <v>1</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>1</v>
+      </c>
+      <c r="O393" t="n">
+        <v>1</v>
+      </c>
+      <c r="P393" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q393" t="inlineStr"/>
+      <c r="R393" t="inlineStr"/>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr"/>
+      <c r="U393" t="inlineStr"/>
+      <c r="V393" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V393"/>
+  <dimension ref="A1:V415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13869,11 +13869,19 @@
       <c r="J185" t="b">
         <v>0</v>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -13893,7 +13901,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -15361,20 +15369,28 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J204" t="b">
-        <v>0</v>
-      </c>
-      <c r="K204" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>05.08.2026</t>
+        </is>
+      </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P204" t="n">
         <v>3</v>
@@ -15391,7 +15407,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
@@ -19545,20 +19561,28 @@
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J258" t="b">
-        <v>0</v>
-      </c>
-      <c r="K258" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P258" t="n">
         <v>1</v>
@@ -19571,7 +19595,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>pasta</t>
+          <t>pasta, medicao</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -21393,7 +21417,7 @@
         <v>0</v>
       </c>
       <c r="P286" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -21557,7 +21581,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21651,7 +21675,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -21749,7 +21773,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -21835,7 +21859,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -21929,7 +21953,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22015,7 +22039,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22101,7 +22125,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22199,7 +22223,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -22609,7 +22633,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -22695,7 +22719,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -22781,7 +22805,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22867,7 +22891,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -25753,7 +25777,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -29628,6 +29652,1742 @@
       <c r="U393" t="inlineStr"/>
       <c r="V393" t="inlineStr"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>1724352</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>086831</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>UMUARAMA</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>35,821</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>35.821</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>R$2.185,08</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J394" t="b">
+        <v>0</v>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
+      <c r="P394" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>AES 08631 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>1724352 - ALNU388002026 - RANA 8940828660</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr"/>
+      <c r="U394" t="inlineStr"/>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 08631 HAGAP_4600026463.pdf', 'ae': '086831'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>1724662I</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>086814</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>201,270</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>201.27</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>R$14.053,14</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J395" t="b">
+        <v>0</v>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>AES 086814 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr"/>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>⚠ AE '086814' em múltiplos projetos: 1724662I, 1735370</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr"/>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086814 HAGAP_4600026463.pdf', 'ae': '086814'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>1735370</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>086814</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>CIDADEGAUCHA</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>201,270</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>201.27</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>R$14.053,14</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J396" t="b">
+        <v>0</v>
+      </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+      <c r="P396" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>AES 086814 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>1735370 01.20264823522120 - AYSLAN TORMENA ANDERSON 25-11-2026</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>⚠ AE '086814' em múltiplos projetos: 1724662I, 1735370</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr"/>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086814 HAGAP_4600026463.pdf', 'ae': '086814'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>1724549</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>086815</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>DECAFEZALDOSUL CENTRO</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>27,985</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>27.985</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>R$1.707,08</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J397" t="b">
+        <v>0</v>
+      </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="P397" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>AES 086815 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>1724549 01.20264114338565 - MUNICIPIO DE CAFEZAL DO SUL 25-09-2026</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr"/>
+      <c r="U397" t="inlineStr"/>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086815 HAGAP_4600026463.pdf', 'ae': '086815'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>1724094I</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>086823</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>LEMOS AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>261,807</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>261.807</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>R$18.172,61</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J398" t="b">
+        <v>0</v>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+      <c r="P398" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>AES 086823 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>1724094I 01.20263803097788 - THAMARA CRISTINA MOTA CREPALDI MALVEZZI 28-12-2026</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>⚠ AE '086823' em múltiplos projetos: 1724094I, 1722985I, 1726737, 1726319, 1724094C, 1722985C</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr"/>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086823 HAGAP_4600026463.pdf', 'ae': '086823'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1722985I</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>086823</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>261,807</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>261.807</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>R$18.172,61</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J399" t="b">
+        <v>0</v>
+      </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0</v>
+      </c>
+      <c r="P399" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>AES 086823 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>1722985I 01.20263965090725 - SIRLEI MARQUES PETERNELLA DE OLIVEIRA 21-12-2026</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>⚠ AE '086823' em múltiplos projetos: 1724094I, 1722985I, 1726737, 1726319, 1724094C, 1722985C</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr"/>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086823 HAGAP_4600026463.pdf', 'ae': '086823'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>1726737</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>086823</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>DETUNEIRASDOOESTE</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>261,807</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>261.807</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>R$18.172,61</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J400" t="b">
+        <v>0</v>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="n">
+        <v>0</v>
+      </c>
+      <c r="O400" t="n">
+        <v>0</v>
+      </c>
+      <c r="P400" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>AES 086823 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>1726737 01.20264267823939 - MUNICIPIO DE TUNEIRAS DO OESTE 04-12-2026</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>⚠ AE '086823' em múltiplos projetos: 1724094I, 1722985I, 1726737, 1726319, 1724094C, 1722985C</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr"/>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086823 HAGAP_4600026463.pdf', 'ae': '086823'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1726319</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>086823</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>261,807</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>261.807</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>R$18.172,61</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J401" t="b">
+        <v>0</v>
+      </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+      <c r="P401" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>AES 086823 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>1726319 01.20264183641162 - C.VALE - COOPERATIVA AGROINDUSTRIAL 23-12-2026</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>⚠ AE '086823' em múltiplos projetos: 1724094I, 1722985I, 1726737, 1726319, 1724094C, 1722985C</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr"/>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086823 HAGAP_4600026463.pdf', 'ae': '086823'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>1724094C</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>086823</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>261,807</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>261.807</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>R$18.172,61</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J402" t="b">
+        <v>0</v>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="n">
+        <v>0</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>AES 086823 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr"/>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>⚠ AE '086823' em múltiplos projetos: 1724094I, 1722985I, 1726737, 1726319, 1724094C, 1722985C</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr"/>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086823 HAGAP_4600026463.pdf', 'ae': '086823'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>1722985C</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>086823</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>261,807</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>261.807</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>R$18.172,61</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J403" t="b">
+        <v>0</v>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="n">
+        <v>0</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>AES 086823 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr"/>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>⚠ AE '086823' em múltiplos projetos: 1724094I, 1722985I, 1726737, 1726319, 1724094C, 1722985C</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr"/>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086823 HAGAP_4600026463.pdf', 'ae': '086823'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1731349</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>086824</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>ATHIER</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2.517,049</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>2517.049</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>15/11/2026</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>R$153.539,98</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J404" t="b">
+        <v>0</v>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0</v>
+      </c>
+      <c r="P404" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>AES 086824 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>1731349 - 1KM - ALNU388242026 - 2522US</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr"/>
+      <c r="U404" t="inlineStr"/>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086824 HAGAP_4600026463.pdf', 'ae': '086824'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>1731354</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>086825</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>PEROBAL</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2.263,979</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>2263.979</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>15/11/2026</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>R$138.102,71</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J405" t="b">
+        <v>0</v>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
+      <c r="P405" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>AES 086825 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>1731354 - - 1,45KM - ALNU388242026 - 2264US</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr"/>
+      <c r="U405" t="inlineStr"/>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086825 HAGAP_4600026463.pdf', 'ae': '086825'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1736375</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>086826</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>IPORA</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2.268,444</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>2268.444</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>15/11/2026</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>R$138.375,08</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J406" t="b">
+        <v>0</v>
+      </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+      <c r="P406" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>AES 086826 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>1736375 ALNU388992026 - RECONDUTORAMENTO - IPORÃ - 2286US</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr"/>
+      <c r="U406" t="inlineStr"/>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086826 HAGAP_4600026463.pdf', 'ae': '086826'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1734584</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>086828</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>MOREIRA AZEVEDO EXECUÇÃO</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>224,069</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>224.069</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>R$17.109,90</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J407" t="b">
+        <v>0</v>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+      <c r="P407" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>AES 086828 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>1734584 - 1734532 ALNU388982026 - BRT ALTONIA</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr"/>
+      <c r="U407" t="inlineStr"/>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086828 HAGAP_4600026463.pdf', 'ae': '086828'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>1734532</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>086829</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>211,757</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>211.757</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>R$16.169,76</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J408" t="b">
+        <v>0</v>
+      </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>AES 086829 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr"/>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr"/>
+      <c r="U408" t="inlineStr"/>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086829 HAGAP_4600026463.pdf', 'ae': '086829'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1724353</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>086830</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>MAICON LUIZ WATHIER</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>42,673</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>42.673</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>R$2.603,05</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J409" t="b">
+        <v>0</v>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>AES 086830 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>1724353 - ALNU388002026 - RANF 8940840095</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr"/>
+      <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086830 HAGAP_4600026463.pdf', 'ae': '086830'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1737272</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>086870</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>156,768</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>156.768</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>R$11.970,80</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J410" t="b">
+        <v>0</v>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>AES 086870 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr"/>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr"/>
+      <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086870 HAGAP_4600026463.pdf', 'ae': '086870'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>1737274</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>086872</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>146,245</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>146.245</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>R$11.167,26</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J411" t="b">
+        <v>0</v>
+      </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>AES 086872 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr"/>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr"/>
+      <c r="U411" t="inlineStr"/>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086872 HAGAP_4600026463.pdf', 'ae': '086872'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1694199</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>086700</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>269,495</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>269.495</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>R$20.578,62</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J412" t="b">
+        <v>0</v>
+      </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>AES_86700_HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>⚠ AE '086700' em múltiplos projetos: 1694199, 1735925</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr"/>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES_86700_HAGAP_4600026463.pdf', 'ae': '086700'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1735925</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>086700</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>269,495</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>269.495</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>R$20.578,62</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J413" t="b">
+        <v>0</v>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>AES_86700_HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>⚠ AE '086700' em múltiplos projetos: 1694199, 1735925</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr"/>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES_86700_HAGAP_4600026463.pdf', 'ae': '086700'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1724662</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>R$6.675,92</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J414" t="b">
+        <v>0</v>
+      </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1724662 01.20264054451862 - ANA MARIA ALVES FREIRE 07-12-2026</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr"/>
+      <c r="U414" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1710287I</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J415" t="b">
+        <v>1</v>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>1</v>
+      </c>
+      <c r="O415" t="n">
+        <v>1</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q415" t="inlineStr"/>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr"/>
+      <c r="U415" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V415"/>
+  <dimension ref="A1:V431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5973,17 +5973,21 @@
       <c r="J63" t="b">
         <v>0</v>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5997,7 +6001,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -6043,7 +6047,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6133,7 +6137,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6253,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -6313,7 +6317,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6403,7 +6407,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6501,7 +6505,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6595,7 +6599,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6681,7 +6685,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6779,7 +6783,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6877,7 +6881,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7477,7 +7481,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10525,24 +10529,32 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -12529,11 +12541,11 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12545,12 +12557,16 @@
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
       <c r="N170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P170" t="n">
         <v>0</v>
@@ -15127,24 +15143,32 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
       <c r="N201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P201" t="n">
         <v>6</v>
@@ -15647,24 +15671,32 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P207" t="n">
         <v>3</v>
@@ -17232,10 +17264,14 @@
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -17404,10 +17440,14 @@
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -18353,7 +18393,7 @@
         <v>0</v>
       </c>
       <c r="P242" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -19499,20 +19539,28 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J257" t="b">
-        <v>0</v>
-      </c>
-      <c r="K257" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P257" t="n">
         <v>0</v>
@@ -19525,7 +19573,7 @@
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -19695,7 +19743,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -19985,7 +20033,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20189,24 +20237,32 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P266" t="n">
         <v>0</v>
@@ -20715,24 +20771,32 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
       <c r="N275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P275" t="n">
         <v>0</v>
@@ -21581,7 +21645,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21675,7 +21739,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -21773,7 +21837,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -21799,7 +21863,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
@@ -21859,7 +21923,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -21953,7 +22017,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22039,7 +22103,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22065,7 +22129,7 @@
         <v>0</v>
       </c>
       <c r="P294" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
@@ -22125,7 +22189,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22223,7 +22287,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -22249,7 +22313,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
@@ -22305,7 +22369,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -22383,7 +22447,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -22469,7 +22533,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -22561,20 +22625,32 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J300" t="b">
-        <v>0</v>
-      </c>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>MULTA-1729786-HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P300" t="n">
         <v>3</v>
@@ -22591,7 +22667,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -22633,7 +22709,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -22719,7 +22795,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -22735,17 +22811,21 @@
       <c r="J302" t="b">
         <v>0</v>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
       </c>
       <c r="P302" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -22759,7 +22839,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T302" t="inlineStr">
@@ -22805,7 +22885,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -22891,7 +22971,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -23349,7 +23429,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23435,7 +23515,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -23533,7 +23613,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -23627,7 +23707,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23971,7 +24051,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24045,7 +24125,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24305,7 +24385,7 @@
         <v>0</v>
       </c>
       <c r="P320" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
@@ -24391,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="P321" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
@@ -24725,17 +24805,21 @@
       <c r="J325" t="b">
         <v>0</v>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O325" t="n">
         <v>0</v>
       </c>
       <c r="P325" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
@@ -24749,7 +24833,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T325" t="inlineStr">
@@ -25369,24 +25453,32 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr"/>
-      <c r="M334" t="inlineStr"/>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
       <c r="N334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P334" t="n">
         <v>3</v>
@@ -26069,7 +26161,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -26151,7 +26243,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -26233,7 +26325,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -26803,7 +26895,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -26881,7 +26973,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -26907,7 +26999,7 @@
         <v>0</v>
       </c>
       <c r="P355" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q355" t="inlineStr">
         <is>
@@ -27399,7 +27491,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -27485,7 +27577,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -27571,7 +27663,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -27657,7 +27749,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -27743,7 +27835,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -27769,7 +27861,7 @@
         <v>0</v>
       </c>
       <c r="P368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -27829,7 +27921,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -27915,7 +28007,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -28807,7 +28899,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -31388,6 +31480,1210 @@
       <c r="U415" t="inlineStr"/>
       <c r="V415" t="inlineStr"/>
     </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>1732157</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>086419</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>55,024</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>55.024</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>R$3.356,46</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J416" t="b">
+        <v>0</v>
+      </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>AES 086419 HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr"/>
+      <c r="U416" t="inlineStr"/>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086419 HAGAP_4600026463.pdf', 'ae': '086419'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1731746</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>086510</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>25,764</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>25.764</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>R$1.571,60</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J417" t="b">
+        <v>0</v>
+      </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>AES 086510 HAGAP 4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr"/>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr"/>
+      <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 086510 HAGAP 4600026463.pdf', 'ae': '086510'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>1718295</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>087128</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>CRUZEIRODOOESTE</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>90,506</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>90.506</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>R$5.520,86</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J418" t="b">
+        <v>0</v>
+      </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="P418" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>AES 87128  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>1718295 NDS 293643 RDU CRUZEIRO DO OESTE HAGAP</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr"/>
+      <c r="U418" t="inlineStr"/>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87128  4600026463 HAGAP.pdf', 'ae': '087128'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1733159</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>087129</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>235,977</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>235.977</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>R$14.394,58</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J419" t="b">
+        <v>0</v>
+      </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>AES 87129  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>1733159 01.20264741063438 - GRAZIELA CRISTINA NOGARA 05-10-2026</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>⚠ AE '087129' em múltiplos projetos: 1733159, 1735868, 1738691, 1738704</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr"/>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87129  4600026463 HAGAP.pdf', 'ae': '087129'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>1735868</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>087129</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>235,977</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>235.977</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>R$14.394,58</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J420" t="b">
+        <v>0</v>
+      </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="n">
+        <v>0</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+      <c r="P420" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>AES 87129  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>1735868 01.20264849812639 - ALESSANDRO SILVA 08-10-2026</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>⚠ AE '087129' em múltiplos projetos: 1733159, 1735868, 1738691, 1738704</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr"/>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87129  4600026463 HAGAP.pdf', 'ae': '087129'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1738691</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>087129</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>DEPEROLA CENTRO</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>235,977</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>235.977</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>R$14.394,58</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J421" t="b">
+        <v>0</v>
+      </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="P421" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>AES 87129  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>1738691 01.20265086269006 - MUNICIPIO DE PEROLA 05-10-2026</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>⚠ AE '087129' em múltiplos projetos: 1733159, 1735868, 1738691, 1738704</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr"/>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87129  4600026463 HAGAP.pdf', 'ae': '087129'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1738704</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>087129</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>DEPEROLA CENTRO</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>235,977</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>235.977</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>R$14.394,58</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J422" t="b">
+        <v>0</v>
+      </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+      <c r="P422" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>AES 87129  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>1738704 01.20265086851377 - MUNICIPIO DE PEROLA 05-10-2026</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>⚠ AE '087129' em múltiplos projetos: 1733159, 1735868, 1738691, 1738704</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr"/>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87129  4600026463 HAGAP.pdf', 'ae': '087129'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1737369I</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>087137</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>866,823</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>866.823</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>R$54.238,29</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J423" t="b">
+        <v>0</v>
+      </c>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>AES 87137  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr"/>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>⚠ AE '087137' em múltiplos projetos: 1737369I, 1738291I, 1740160I, 1737369C, 1740160C</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr"/>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87137  4600026463 HAGAP.pdf', 'ae': '087137'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>1738291I</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>087137</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>866,823</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>866.823</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>R$54.238,29</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J424" t="b">
+        <v>0</v>
+      </c>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" t="n">
+        <v>0</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>AES 87137  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr"/>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>⚠ AE '087137' em múltiplos projetos: 1737369I, 1738291I, 1740160I, 1737369C, 1740160C</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr"/>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87137  4600026463 HAGAP.pdf', 'ae': '087137'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>1740160I</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>087137</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>866,823</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>866.823</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>R$54.238,29</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J425" t="b">
+        <v>0</v>
+      </c>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="n">
+        <v>0</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>AES 87137  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr"/>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>⚠ AE '087137' em múltiplos projetos: 1737369I, 1738291I, 1740160I, 1737369C, 1740160C</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr"/>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87137  4600026463 HAGAP.pdf', 'ae': '087137'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>1737369C</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>087137</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>866,823</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>866.823</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>R$54.238,29</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J426" t="b">
+        <v>0</v>
+      </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>AES 87137  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr"/>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>⚠ AE '087137' em múltiplos projetos: 1737369I, 1738291I, 1740160I, 1737369C, 1740160C</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr"/>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87137  4600026463 HAGAP.pdf', 'ae': '087137'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>1740160C</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>087137</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>866,823</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>866.823</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>R$54.238,29</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J427" t="b">
+        <v>0</v>
+      </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="n">
+        <v>0</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>AES 87137  4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr"/>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>⚠ AE '087137' em múltiplos projetos: 1737369I, 1738291I, 1740160I, 1737369C, 1740160C</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr"/>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87137  4600026463 HAGAP.pdf', 'ae': '087137'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>1726581</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>087138</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>49,222</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>49.222</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>13/11/2026</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>R$3.758,59</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J428" t="b">
+        <v>0</v>
+      </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>AES 87138 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>1726581</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr"/>
+      <c r="U428" t="inlineStr"/>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87138 4600026463 HAGAP.pdf', 'ae': '087138'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>1686607C</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="n">
+        <v>0</v>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J429" t="b">
+        <v>1</v>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>1</v>
+      </c>
+      <c r="O429" t="n">
+        <v>1</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q429" t="inlineStr"/>
+      <c r="R429" t="inlineStr"/>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr"/>
+      <c r="U429" t="inlineStr"/>
+      <c r="V429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>1686607I</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="n">
+        <v>0</v>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J430" t="b">
+        <v>1</v>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>1</v>
+      </c>
+      <c r="O430" t="n">
+        <v>1</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q430" t="inlineStr"/>
+      <c r="R430" t="inlineStr"/>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr"/>
+      <c r="U430" t="inlineStr"/>
+      <c r="V430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>1706284</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="n">
+        <v>0</v>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J431" t="b">
+        <v>0</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="n">
+        <v>1</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q431" t="inlineStr"/>
+      <c r="R431" t="inlineStr"/>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr"/>
+      <c r="U431" t="inlineStr"/>
+      <c r="V431" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V431"/>
+  <dimension ref="A1:V505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,7 +681,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1369,11 +1369,15 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1393,7 +1397,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1693,11 +1697,15 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1717,7 +1725,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1947,11 +1955,15 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1967,7 +1979,7 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2419,7 +2431,11 @@
           <t>083978</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>414,483</t>
@@ -2461,17 +2477,21 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>AES 83978 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1719094 01.20263603048714 - VERA LUCIA ALEXANDRINO</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, pasta</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2710,10 +2730,14 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2845,7 +2869,11 @@
           <t>083980</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RESPONDIDA PARTICIPACAOFINANCEIRA</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>1.080,951</t>
@@ -2899,17 +2927,21 @@
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>AES 83980 4600026463 HAGAP.pdf</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1711489 01.20263155072364 - WESLEY FERREIRA DA SILVA</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>ae, medicao</t>
+          <t>ae, medicao, pasta</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -5509,24 +5541,32 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>4</v>
@@ -6047,7 +6087,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6137,7 +6177,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6231,7 +6271,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6317,7 +6357,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6407,7 +6447,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6505,7 +6545,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6599,7 +6639,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6685,7 +6725,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6783,7 +6823,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6881,7 +6921,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6891,24 +6931,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
@@ -8157,11 +8205,11 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -8173,12 +8221,16 @@
           <t>17/07/2026</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -8309,10 +8361,18 @@
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CAMPO MOURÃO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11,020</t>
+        </is>
+      </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>11.02</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -8347,13 +8407,17 @@
         <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1704952 HAGAP</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>medicao</t>
+          <t>medicao, pasta</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9003,24 +9067,32 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -13145,7 +13217,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13239,7 +13311,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13333,7 +13405,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13419,7 +13491,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14347,7 +14419,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -14363,11 +14435,15 @@
       <c r="J192" t="b">
         <v>0</v>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -14387,7 +14463,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -14429,7 +14505,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -14511,7 +14587,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14875,7 +14951,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14965,7 +15041,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -14981,11 +15057,15 @@
       <c r="J199" t="b">
         <v>0</v>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -15005,7 +15085,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -15051,7 +15131,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15067,11 +15147,15 @@
       <c r="J200" t="b">
         <v>0</v>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -15091,7 +15175,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -15859,23 +15943,31 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J209" t="b">
-        <v>0</v>
-      </c>
-      <c r="K209" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P209" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -15889,7 +15981,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
@@ -16054,10 +16146,14 @@
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -16139,11 +16235,15 @@
       <c r="J212" t="b">
         <v>0</v>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -16163,7 +16263,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
@@ -17354,10 +17454,14 @@
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -18377,20 +18481,32 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J242" t="b">
-        <v>0</v>
-      </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>MULTA - 1726388 - HAGAP - 20-08-2026.pdf</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P242" t="n">
         <v>6</v>
@@ -18407,7 +18523,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
@@ -18469,11 +18585,15 @@
       <c r="J243" t="b">
         <v>0</v>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -18493,7 +18613,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
@@ -19468,10 +19588,14 @@
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -21465,20 +21589,28 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J286" t="b">
-        <v>0</v>
-      </c>
-      <c r="K286" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P286" t="n">
         <v>5</v>
@@ -21495,7 +21627,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -21847,20 +21979,32 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J291" t="b">
-        <v>0</v>
-      </c>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
+        </is>
+      </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P291" t="n">
         <v>5</v>
@@ -21877,7 +22021,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -22113,20 +22257,32 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J294" t="b">
-        <v>0</v>
-      </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>MULTA - 1729300 - HAGAP - 20-08-2026.pdf</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P294" t="n">
         <v>7</v>
@@ -22143,7 +22299,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
@@ -22369,7 +22525,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -22447,7 +22603,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -22533,7 +22689,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -22719,20 +22875,28 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J301" t="b">
-        <v>0</v>
-      </c>
-      <c r="K301" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P301" t="n">
         <v>5</v>
@@ -22749,7 +22913,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T301" t="inlineStr">
@@ -22895,20 +23059,28 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J303" t="b">
-        <v>0</v>
-      </c>
-      <c r="K303" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
       <c r="N303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P303" t="n">
         <v>5</v>
@@ -22925,7 +23097,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T303" t="inlineStr">
@@ -23065,7 +23237,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -23159,7 +23331,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -23249,7 +23421,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -23429,7 +23601,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23445,17 +23617,21 @@
       <c r="J309" t="b">
         <v>0</v>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O309" t="n">
         <v>0</v>
       </c>
       <c r="P309" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -23469,7 +23645,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T309" t="inlineStr">
@@ -23515,7 +23691,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -23613,7 +23789,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -23707,7 +23883,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -23793,7 +23969,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23809,11 +23985,15 @@
       <c r="J313" t="b">
         <v>0</v>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O313" t="n">
         <v>0</v>
@@ -23833,7 +24013,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T313" t="inlineStr">
@@ -23879,7 +24059,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23969,7 +24149,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -23985,17 +24165,21 @@
       <c r="J315" t="b">
         <v>0</v>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
       </c>
       <c r="P315" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -24009,7 +24193,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T315" t="inlineStr">
@@ -24051,7 +24235,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24067,11 +24251,15 @@
       <c r="J316" t="b">
         <v>0</v>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O316" t="n">
         <v>0</v>
@@ -24087,7 +24275,7 @@
       <c r="R316" t="inlineStr"/>
       <c r="S316" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -24125,7 +24313,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24199,7 +24387,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24277,7 +24465,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -24359,7 +24547,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -24369,20 +24557,28 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J320" t="b">
-        <v>0</v>
-      </c>
-      <c r="K320" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
       <c r="N320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P320" t="n">
         <v>5</v>
@@ -24399,7 +24595,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T320" t="inlineStr">
@@ -24445,7 +24641,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -24461,11 +24657,15 @@
       <c r="J321" t="b">
         <v>0</v>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O321" t="n">
         <v>0</v>
@@ -24485,7 +24685,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T321" t="inlineStr">
@@ -24531,7 +24731,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24547,17 +24747,21 @@
       <c r="J322" t="b">
         <v>0</v>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O322" t="n">
         <v>0</v>
       </c>
       <c r="P322" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
@@ -24571,7 +24775,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T322" t="inlineStr">
@@ -24617,7 +24821,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -24633,11 +24837,15 @@
       <c r="J323" t="b">
         <v>0</v>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O323" t="n">
         <v>0</v>
@@ -24657,7 +24865,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T323" t="inlineStr">
@@ -24703,7 +24911,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -24729,7 +24937,7 @@
         <v>0</v>
       </c>
       <c r="P324" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -24789,7 +24997,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -24879,7 +25087,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -24905,7 +25113,7 @@
         <v>0</v>
       </c>
       <c r="P326" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -24954,8 +25162,16 @@
       <c r="E327" t="n">
         <v>99.93000000000001</v>
       </c>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
@@ -24975,7 +25191,7 @@
         <v>0</v>
       </c>
       <c r="P327" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q327" t="inlineStr"/>
       <c r="R327" t="inlineStr">
@@ -25023,7 +25239,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -25259,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="P331" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
@@ -25555,7 +25771,7 @@
         <v>0</v>
       </c>
       <c r="P335" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q335" t="inlineStr"/>
       <c r="R335" t="inlineStr">
@@ -25869,7 +26085,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -26007,20 +26223,28 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J343" t="b">
-        <v>0</v>
-      </c>
-      <c r="K343" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr"/>
-      <c r="M343" t="inlineStr"/>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
       <c r="N343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P343" t="n">
         <v>0</v>
@@ -26033,7 +26257,7 @@
       <c r="R343" t="inlineStr"/>
       <c r="S343" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T343" t="inlineStr">
@@ -26079,7 +26303,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -26177,11 +26401,15 @@
       <c r="J345" t="b">
         <v>0</v>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O345" t="n">
         <v>0</v>
@@ -26201,7 +26429,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -26259,11 +26487,15 @@
       <c r="J346" t="b">
         <v>0</v>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="inlineStr"/>
       <c r="N346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O346" t="n">
         <v>0</v>
@@ -26283,7 +26515,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -26341,11 +26573,15 @@
       <c r="J347" t="b">
         <v>0</v>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O347" t="n">
         <v>0</v>
@@ -26365,7 +26601,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -26423,11 +26659,15 @@
       <c r="J348" t="b">
         <v>0</v>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr"/>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O348" t="n">
         <v>0</v>
@@ -26447,7 +26687,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -26505,11 +26745,15 @@
       <c r="J349" t="b">
         <v>0</v>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr"/>
       <c r="N349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O349" t="n">
         <v>0</v>
@@ -26529,7 +26773,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T349" t="inlineStr">
@@ -26911,11 +27155,15 @@
       <c r="J354" t="b">
         <v>0</v>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr"/>
       <c r="N354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O354" t="n">
         <v>0</v>
@@ -26931,7 +27179,7 @@
       <c r="R354" t="inlineStr"/>
       <c r="S354" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -26983,20 +27231,28 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J355" t="b">
-        <v>0</v>
-      </c>
-      <c r="K355" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr"/>
-      <c r="M355" t="inlineStr"/>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
       <c r="N355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P355" t="n">
         <v>8</v>
@@ -27013,7 +27269,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T355" t="inlineStr"/>
@@ -27069,7 +27325,7 @@
         <v>0</v>
       </c>
       <c r="P356" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q356" t="inlineStr"/>
       <c r="R356" t="inlineStr">
@@ -27305,13 +27561,29 @@
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>CIT</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>232,940</t>
+        </is>
+      </c>
       <c r="E361" t="n">
-        <v>0</v>
-      </c>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
+        <v>232.94</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
@@ -27335,13 +27607,17 @@
         <v>0</v>
       </c>
       <c r="P361" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q361" t="inlineStr"/>
-      <c r="R361" t="inlineStr"/>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>1707182 1643306- I-25-0402603</t>
+        </is>
+      </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>medicao</t>
+          <t>medicao, pasta</t>
         </is>
       </c>
       <c r="T361" t="inlineStr"/>
@@ -28635,7 +28911,7 @@
         <v>0</v>
       </c>
       <c r="P377" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
@@ -28688,10 +28964,14 @@
           <t>29/07/2026</t>
         </is>
       </c>
-      <c r="L378" t="inlineStr"/>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O378" t="n">
         <v>0</v>
@@ -28925,7 +29205,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q382" t="inlineStr">
         <is>
@@ -28981,7 +29261,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -29063,7 +29343,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -29145,7 +29425,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -29231,7 +29511,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -29247,11 +29527,15 @@
       <c r="J386" t="b">
         <v>0</v>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr"/>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O386" t="n">
         <v>0</v>
@@ -29271,7 +29555,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T386" t="inlineStr">
@@ -29313,7 +29597,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -29395,7 +29679,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -29411,11 +29695,15 @@
       <c r="J388" t="b">
         <v>0</v>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr"/>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O388" t="n">
         <v>0</v>
@@ -29435,7 +29723,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T388" t="inlineStr">
@@ -29477,7 +29765,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -29493,11 +29781,15 @@
       <c r="J389" t="b">
         <v>0</v>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr"/>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O389" t="n">
         <v>0</v>
@@ -29513,7 +29805,7 @@
       <c r="R389" t="inlineStr"/>
       <c r="S389" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T389" t="inlineStr">
@@ -30021,7 +30313,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -30301,7 +30593,7 @@
         <v>0</v>
       </c>
       <c r="P400" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -31099,11 +31391,15 @@
       <c r="J410" t="b">
         <v>0</v>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr"/>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O410" t="n">
         <v>0</v>
@@ -31119,7 +31415,7 @@
       <c r="R410" t="inlineStr"/>
       <c r="S410" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T410" t="inlineStr"/>
@@ -31173,11 +31469,15 @@
       <c r="J411" t="b">
         <v>0</v>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr"/>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O411" t="n">
         <v>0</v>
@@ -31193,7 +31493,7 @@
       <c r="R411" t="inlineStr"/>
       <c r="S411" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T411" t="inlineStr"/>
@@ -31231,7 +31531,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -31309,7 +31609,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -31491,7 +31791,11 @@
           <t>086419</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
           <t>55,024</t>
@@ -31507,7 +31811,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -31523,27 +31827,35 @@
       <c r="J416" t="b">
         <v>0</v>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr"/>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O416" t="n">
         <v>0</v>
       </c>
       <c r="P416" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
           <t>AES 086419 HAGAP_4600026463.pdf</t>
         </is>
       </c>
-      <c r="R416" t="inlineStr"/>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>1732157 - JORGE MANUEL</t>
+        </is>
+      </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T416" t="inlineStr"/>
@@ -31565,7 +31877,11 @@
           <t>086510</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
       <c r="D417" t="inlineStr">
         <is>
           <t>25,764</t>
@@ -31581,7 +31897,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -31597,27 +31913,35 @@
       <c r="J417" t="b">
         <v>0</v>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr"/>
       <c r="M417" t="inlineStr"/>
       <c r="N417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O417" t="n">
         <v>0</v>
       </c>
       <c r="P417" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
           <t>AES 086510 HAGAP 4600026463.pdf</t>
         </is>
       </c>
-      <c r="R417" t="inlineStr"/>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>1731746 - VALDINEI VERRES GOMES</t>
+        </is>
+      </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -31741,7 +32065,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -31827,7 +32151,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -31913,7 +32237,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -31999,7 +32323,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -32684,6 +33008,5854 @@
       <c r="U431" t="inlineStr"/>
       <c r="V431" t="inlineStr"/>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>1727889</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>087168</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>203,931</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>203.931</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>R$13.987,44</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J432" t="b">
+        <v>0</v>
+      </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="P432" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>AES 87168 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>1727889 01.20264336423435 - AGROPECUARIA JOAO DE BARRO LTDA ME 25-09-2026</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>⚠ AE '087168' em múltiplos projetos: 1727889, 1731938, 1735367</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr"/>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87168 4600026463 HAGAP.pdf', 'ae': '087168'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>1731938</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>087168</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>DEJAPURA</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>203,931</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>203.931</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>R$13.987,44</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J433" t="b">
+        <v>0</v>
+      </c>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>AES 87168 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>1731938 01.20264625431984 - MAQUEA MAQUEA LTDA 25-09-2026</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>⚠ AE '087168' em múltiplos projetos: 1727889, 1731938, 1735367</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr"/>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87168 4600026463 HAGAP.pdf', 'ae': '087168'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>1735367</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>087168</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>203,931</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>203.931</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>R$13.987,44</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J434" t="b">
+        <v>0</v>
+      </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="P434" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>AES 87168 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>1735367 01.20264841981476 - JUNICLEBER DA SILVA 25-09-2026</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>⚠ AE '087168' em múltiplos projetos: 1727889, 1731938, 1735367</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr"/>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87168 4600026463 HAGAP.pdf', 'ae': '087168'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1738690</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>087169</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>DEPEROLA CENTRO</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>130,796</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>130.796</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>R$7.978,55</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J435" t="b">
+        <v>0</v>
+      </c>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>AES 87169 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>1738690 01.20265084893599 - MUNICIPIO DE PEROLA 04-12-2026</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr"/>
+      <c r="U435" t="inlineStr"/>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87169 4600026463 HAGAP.pdf', 'ae': '087169'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>1737088</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>CORBELIA</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J436" t="b">
+        <v>0</v>
+      </c>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="P436" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>1737088 PARTE 1 - ALOC384602026 DESLOCAR BRT 037 - CFL CBL 151 US</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr"/>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1737089</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>CORBELIA</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J437" t="b">
+        <v>0</v>
+      </c>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>1737089 PARTE 2 - ALOC384602026 DESLOCAR BRT 042</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr"/>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>1730312</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>CAFELANDIA</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J438" t="b">
+        <v>0</v>
+      </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>1730312 - PARTE 4 - BRT NOVO 150A</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr"/>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>1730313</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>CAFELANDIA</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J439" t="b">
+        <v>0</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="n">
+        <v>1</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>1730313 PARTE 5 ALOC384602026 - BRT NOVO 150A</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>ae, pasta, medicao</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr"/>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>1741124</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>BRTURGENTE-PLANILHACOPACOL</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J440" t="b">
+        <v>0</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="n">
+        <v>1</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>1741124 - ALOC 392762026 - CFL</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>ae, pasta, medicao</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr"/>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>1741136</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>CASCAVEL</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J441" t="b">
+        <v>0</v>
+      </c>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>1741136 PARTE 6 - ITEM 8 - ALOC408502027 DESLOCAR RT886 - 110 US</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr"/>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>1741131</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>S SUBESTAÇÕES ALIMENTADORES VÍNCULOS</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J442" t="b">
+        <v>0</v>
+      </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>1741131 PARTE 7.1 - ITEM 9 - ALOC408502027 DESLOCAR RT020 -  CEL TUP 103 US</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr"/>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>1740643</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>S SUBESTAÇÕES ALIMENTADORES VÍNCULOS</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J443" t="b">
+        <v>0</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="n">
+        <v>1</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>1740643 PARTE 7.2 - ITEM 9 - ALOC408502027 BRT NOVO 200A - 146 US</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>ae, pasta, medicao</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr"/>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>1741248</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>087243</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>CASCAVEL</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>1.483,617</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>1483.617</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>R$113.288,94</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J444" t="b">
+        <v>0</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="n">
+        <v>1</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>AES 87243 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>1741248 PARTE 8 - ITEM 10 - ALOC408502027 BRT NOVO 200A - 159 US</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>ae, pasta, medicao</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>⚠ AE '087243' em múltiplos projetos: 1737088, 1737089, 1730312, 1730313, 1741124, 1741136, 1741131, 1740643, 1741248</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr"/>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87243 4600026463 HAGAP.pdf', 'ae': '087243'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>1736228</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>087084</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>368,027</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>368.027</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>R$28.102,54</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J445" t="b">
+        <v>0</v>
+      </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>AES_87084_HAGAP_4600026463.pdf</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr"/>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr"/>
+      <c r="U445" t="inlineStr"/>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES_87084_HAGAP_4600026463.pdf', 'ae': '087084'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1688921</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MOS</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="n">
+        <v>0</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>R$ 12.550,55</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J446" t="b">
+        <v>0</v>
+      </c>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q446" t="inlineStr"/>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>1688921 - 01.20251462471321 - COMPANHIA DE SANEAMENTO DO PARANA SANEPAR</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr"/>
+      <c r="U446" t="inlineStr"/>
+      <c r="V446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>1726019</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="n">
+        <v>0</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J447" t="b">
+        <v>0</v>
+      </c>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q447" t="inlineStr"/>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>1726019</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr"/>
+      <c r="U447" t="inlineStr"/>
+      <c r="V447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>1726043</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>087326</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>5.772,350</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>5772.35</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>30.12.2026</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>R$440.776,63</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J448" t="b">
+        <v>0</v>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+      <c r="P448" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>AES 87326 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>1726043</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>⚠ AE '087326' em múltiplos projetos: 1726043, 1726051, 1726055</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr"/>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87326 4600026463 HAGAP.pdf', 'ae': '087326'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1726051</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>087326</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>R SA</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>5.772,350</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>5772.35</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>R$440.776,63</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J449" t="b">
+        <v>0</v>
+      </c>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
+      <c r="N449" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+      <c r="P449" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>AES 87326 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>1726051</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>⚠ AE '087326' em múltiplos projetos: 1726043, 1726051, 1726055</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr"/>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87326 4600026463 HAGAP.pdf', 'ae': '087326'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>1726055</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>087326</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>TUNEIRAS DO OESTE</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>5.772,350</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>5772.35</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>31.12.2026</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>R$440.776,63</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J450" t="b">
+        <v>0</v>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="P450" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>AES 87326 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>1726055</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>⚠ AE '087326' em múltiplos projetos: 1726043, 1726051, 1726055</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr"/>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87326 4600026463 HAGAP.pdf', 'ae': '087326'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>1726914</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>087305</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>SEITENFUS AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>820,307</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>820.307</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>02.06.2028</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>R$ 30.876,85</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J451" t="b">
+        <v>0</v>
+      </c>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
+      <c r="N451" t="n">
+        <v>0</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="P451" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>AES 87305 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>1726914 01.20264292142299 - MARCELO RODRIGUES DE OLIVEIRA 16-08-2027</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>⚠ AE '087305' em múltiplos projetos: 1726914, 1731395, 1732558</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr"/>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87305 4600026463 HAGAP.pdf', 'ae': '087305'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>1727530</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="n">
+        <v>0</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>06.11.2026</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J452" t="b">
+        <v>0</v>
+      </c>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
+      <c r="N452" t="n">
+        <v>0</v>
+      </c>
+      <c r="O452" t="n">
+        <v>0</v>
+      </c>
+      <c r="P452" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q452" t="inlineStr"/>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>1727530 01.20264223210164 - APARECIDA DE OLIVEIRA MENEZES 02-10-2026</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr"/>
+      <c r="U452" t="inlineStr"/>
+      <c r="V452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>1729798</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>087244</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>246,050</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>246.05</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>11.06.2027</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>R$15.009,04</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J453" t="b">
+        <v>0</v>
+      </c>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+      <c r="P453" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>AES 87244 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>1729798 01.20264405736784 - LEONARDO ALAN DA SILVA 13-10-2026</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>⚠ AE '087244' em múltiplos projetos: 1729798, 1736577, 1738686</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr"/>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87244 4600026463 HAGAP.pdf', 'ae': '087244'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>1731395</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>087305</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>DEXAMBRE CENTRO</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>820,307</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>820.307</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>24.01.2027</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>R$14.960,29</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J454" t="b">
+        <v>0</v>
+      </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
+      <c r="P454" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>AES 87305 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>1731395 01.20264581776096 - MUNICIPIO DE XAMBRE 14-12-2026</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>⚠ AE '087305' em múltiplos projetos: 1726914, 1731395, 1732558</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr"/>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87305 4600026463 HAGAP.pdf', 'ae': '087305'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>1731944</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="n">
+        <v>0</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>30.06.2027</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J455" t="b">
+        <v>0</v>
+      </c>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+      <c r="P455" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q455" t="inlineStr"/>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>1731944 01.20264663913344 - NEUZA SOARES DA SILVA FIGUEIREDO 05-10-2026</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr"/>
+      <c r="U455" t="inlineStr"/>
+      <c r="V455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>1732558</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>087305</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>DECIANORTE</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>820,307</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>820.307</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>06.10.2027</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>R$43.905,47</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J456" t="b">
+        <v>0</v>
+      </c>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="n">
+        <v>0</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+      <c r="P456" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>AES 87305 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>1732558 01.20264691799564 - MUNICIPIO DE CIANORTE 09-08-2027</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>⚠ AE '087305' em múltiplos projetos: 1726914, 1731395, 1732558</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr"/>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87305 4600026463 HAGAP.pdf', 'ae': '087305'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>1733161</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>ANUNCIACAO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" t="n">
+        <v>0</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>09.07.2027</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J457" t="b">
+        <v>0</v>
+      </c>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0</v>
+      </c>
+      <c r="P457" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q457" t="inlineStr"/>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>1733161 01.20264743093901 - MITRA DIOCESANA DE UMUARAMA 01-10-2026</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr"/>
+      <c r="U457" t="inlineStr"/>
+      <c r="V457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>1734515</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>CANTELLI AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" t="n">
+        <v>0</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>22.07.2027</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J458" t="b">
+        <v>0</v>
+      </c>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+      <c r="P458" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q458" t="inlineStr"/>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>1734515 01.20264813063217 - CLAUDIA FORMAGGI SALES 28-09-2026</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr"/>
+      <c r="U458" t="inlineStr"/>
+      <c r="V458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>1734968</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="n">
+        <v>0</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>14.07.2027</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J459" t="b">
+        <v>0</v>
+      </c>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q459" t="inlineStr"/>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>1734968 01.20264779684364 - VALDECIR LOPES NOGUEIRA 28-09-2026</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr"/>
+      <c r="U459" t="inlineStr"/>
+      <c r="V459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>1735369</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="n">
+        <v>0</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>15.07.2027</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J460" t="b">
+        <v>0</v>
+      </c>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
+      <c r="N460" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+      <c r="P460" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q460" t="inlineStr"/>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>1735369 01.20264843879240 - CLAUDIA CRISTIANE JEDLICZKA 01-10-2026</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr"/>
+      <c r="U460" t="inlineStr"/>
+      <c r="V460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>1736577</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>087244</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>246,050</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>246.05</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>28.07.2027</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>R$ 49.097,23</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J461" t="b">
+        <v>0</v>
+      </c>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="P461" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>AES 87244 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>1736577 01.20264872362329 - MARCELO FRAZATTO 15-10-2026</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>⚠ AE '087244' em múltiplos projetos: 1729798, 1736577, 1738686</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr"/>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87244 4600026463 HAGAP.pdf', 'ae': '087244'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>1737369</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" t="n">
+        <v>0</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J462" t="b">
+        <v>0</v>
+      </c>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+      <c r="P462" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q462" t="inlineStr"/>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>1737369 UC 86719939_CTO 8940821568 _ SS 20264997727078</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr"/>
+      <c r="U462" t="inlineStr"/>
+      <c r="V462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>1738291</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" t="n">
+        <v>0</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J463" t="b">
+        <v>0</v>
+      </c>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
+      <c r="N463" t="n">
+        <v>0</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0</v>
+      </c>
+      <c r="P463" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q463" t="inlineStr"/>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>1738291 UC 16928741_CTO 8940802497 _ SS 20265101224680</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr"/>
+      <c r="U463" t="inlineStr"/>
+      <c r="V463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>1738686</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>087244</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>246,050</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>246.05</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>30.12.2027</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>R$15.009,04</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J464" t="b">
+        <v>0</v>
+      </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" t="n">
+        <v>0</v>
+      </c>
+      <c r="P464" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>AES 87244 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>1738686 01.20264998579531 - RUBENS GAZINI 13-10-2026</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>⚠ AE '087244' em múltiplos projetos: 1729798, 1736577, 1738686</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr"/>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87244 4600026463 HAGAP.pdf', 'ae': '087244'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>1738714</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" t="n">
+        <v>0</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>31.07.2027</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>R$2.235,77</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J465" t="b">
+        <v>0</v>
+      </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="n">
+        <v>0</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0</v>
+      </c>
+      <c r="P465" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q465" t="inlineStr"/>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>1738714 01.20265040372526 - EMME ADMINISTRADORA DE IMOVEIS LTDA 28-09-2026</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr"/>
+      <c r="U465" t="inlineStr"/>
+      <c r="V465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>1740160</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>GLOSSÁRIO</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" t="n">
+        <v>0</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J466" t="b">
+        <v>0</v>
+      </c>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" t="n">
+        <v>0</v>
+      </c>
+      <c r="P466" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q466" t="inlineStr"/>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>1740160 UC 91461464_CTO 8940821523_ SS 20264997360095</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr"/>
+      <c r="U466" t="inlineStr"/>
+      <c r="V466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1694264</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" t="n">
+        <v>0</v>
+      </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J467" t="b">
+        <v>0</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>1694264 BMD Parcial.pdf</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="n">
+        <v>1</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0</v>
+      </c>
+      <c r="P467" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q467" t="inlineStr"/>
+      <c r="R467" t="inlineStr"/>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr"/>
+      <c r="U467" t="inlineStr"/>
+      <c r="V467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>1697210I</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" t="n">
+        <v>0</v>
+      </c>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J468" t="b">
+        <v>1</v>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="N468" t="n">
+        <v>2</v>
+      </c>
+      <c r="O468" t="n">
+        <v>2</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q468" t="inlineStr"/>
+      <c r="R468" t="inlineStr"/>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr"/>
+      <c r="U468" t="inlineStr"/>
+      <c r="V468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>1705034</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" t="n">
+        <v>0</v>
+      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J469" t="b">
+        <v>0</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>MULTA - 1705034 - HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="n">
+        <v>2</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q469" t="inlineStr"/>
+      <c r="R469" t="inlineStr"/>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr"/>
+      <c r="U469" t="inlineStr"/>
+      <c r="V469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1629477I</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="n">
+        <v>0</v>
+      </c>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="J470" t="b">
+        <v>1</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="N470" t="n">
+        <v>1</v>
+      </c>
+      <c r="O470" t="n">
+        <v>1</v>
+      </c>
+      <c r="P470" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q470" t="inlineStr"/>
+      <c r="R470" t="inlineStr"/>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr"/>
+      <c r="U470" t="inlineStr"/>
+      <c r="V470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>1713916</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="n">
+        <v>0</v>
+      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J471" t="b">
+        <v>0</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
+      <c r="N471" t="n">
+        <v>1</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q471" t="inlineStr"/>
+      <c r="R471" t="inlineStr"/>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr"/>
+      <c r="U471" t="inlineStr"/>
+      <c r="V471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>1721893</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>087478</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>225,733</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>225.733</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>R$17.236,97</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J472" t="b">
+        <v>0</v>
+      </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
+      <c r="P472" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>AES 87478 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>1721893 01.20263889580142 - EPR PARANA S.A 16.09.2026</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr"/>
+      <c r="U472" t="inlineStr"/>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87478 4600026463 HAGAP.pdf', 'ae': '087478'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>1742470</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>087479</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>UMUARAMA</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>1.488,589</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>1488.589</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>R$113.668,65</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J473" t="b">
+        <v>0</v>
+      </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="n">
+        <v>0</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0</v>
+      </c>
+      <c r="P473" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>AES 87479 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>1742470 ALNU328842021 URGENTE 30-09-2026</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr"/>
+      <c r="U473" t="inlineStr"/>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87479 4600026463 HAGAP.pdf', 'ae': '087479'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>1737782</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>087481</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>93,959</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>93.959</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>R$7.174,70</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J474" t="b">
+        <v>0</v>
+      </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
+      <c r="P474" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>AES 87481 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>1737782 01.20265007452480 - EDSON BATISTA BORGES 22-10-2026</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>⚠ AE '087481' em múltiplos projetos: 1737782, 1738053, 1738729</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr"/>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87481 4600026463 HAGAP.pdf', 'ae': '087481'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>1738053</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>087481</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>93,959</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>93.959</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>R$7.174,70</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J475" t="b">
+        <v>0</v>
+      </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="P475" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>AES 87481 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>1738053 01.20265036964471 - CRARIVALDO BAILO 22-10-2026</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>⚠ AE '087481' em múltiplos projetos: 1737782, 1738053, 1738729</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr"/>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87481 4600026463 HAGAP.pdf', 'ae': '087481'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>1738729</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>087481</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>LEMOS AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>93,959</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>93.959</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>R$7.174,70</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J476" t="b">
+        <v>0</v>
+      </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="P476" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>AES 87481 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>1738729 01.20265106765421 - GUILHERME FRASSON 19-10-2026</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>⚠ AE '087481' em múltiplos projetos: 1737782, 1738053, 1738729</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr"/>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87481 4600026463 HAGAP.pdf', 'ae': '087481'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>1730650</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>087508</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>204,786</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>204.786</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>R$12.491,94</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J477" t="b">
+        <v>0</v>
+      </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
+      <c r="P477" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>AES 87508 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>1730650 01.20264544816015 - ODAIR JOSE GAIARI 23-10-2026</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>⚠ AE '087508' em múltiplos projetos: 1730650, 1737279, 1738130</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr"/>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87508 4600026463 HAGAP.pdf', 'ae': '087508'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>1737279</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>087508</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>DESAOMANOELDOPARANA CENTRO</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>204,786</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>204.786</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>R$12.491,94</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J478" t="b">
+        <v>0</v>
+      </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="n">
+        <v>0</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
+      <c r="P478" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>AES 87508 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>1737279 01.20264977365087 - MUNICIPIO DE SAO MANOEL DO PARANA 19-10-2026</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>⚠ AE '087508' em múltiplos projetos: 1730650, 1737279, 1738130</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr"/>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87508 4600026463 HAGAP.pdf', 'ae': '087508'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>1738130</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>087508</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>DECIDADEGAUCHA</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>204,786</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>204.786</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>R$12.491,94</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J479" t="b">
+        <v>0</v>
+      </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="n">
+        <v>0</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
+      <c r="P479" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>AES 87508 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>1738130 01.20265034341548 - MUNICIPIO DE CIDADE GAUCHA 23-10-2026</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>⚠ AE '087508' em múltiplos projetos: 1730650, 1737279, 1738130</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr"/>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87508 4600026463 HAGAP.pdf', 'ae': '087508'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>1737374</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>087513</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>385,335</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>385.335</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>R$29.424,17</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J480" t="b">
+        <v>0</v>
+      </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="n">
+        <v>0</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0</v>
+      </c>
+      <c r="P480" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>AES 87513 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr"/>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>⚠ AE '087513' em múltiplos projetos: 1737374, 1738942, 1739010, 1739166</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr"/>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87513 4600026463 HAGAP.pdf', 'ae': '087513'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1738942</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>087513</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>385,335</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>385.335</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>R$29.424,17</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J481" t="b">
+        <v>0</v>
+      </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="n">
+        <v>0</v>
+      </c>
+      <c r="O481" t="n">
+        <v>0</v>
+      </c>
+      <c r="P481" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>AES 87513 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>1738942 - 3-112,5KVA - 89180L6690 - FOR</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>⚠ AE '087513' em múltiplos projetos: 1737374, 1738942, 1739010, 1739166</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr"/>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87513 4600026463 HAGAP.pdf', 'ae': '087513'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>1739010</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>087513</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>385,335</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>385.335</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>R$29.424,17</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J482" t="b">
+        <v>0</v>
+      </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" t="n">
+        <v>0</v>
+      </c>
+      <c r="P482" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>AES 87513 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>1739010 - 3-112,5KVA - 89180L7282 - FOR</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>⚠ AE '087513' em múltiplos projetos: 1737374, 1738942, 1739010, 1739166</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr"/>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87513 4600026463 HAGAP.pdf', 'ae': '087513'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>1739166</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>087513</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>385,335</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>385.335</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>R$29.424,17</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J483" t="b">
+        <v>0</v>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="n">
+        <v>0</v>
+      </c>
+      <c r="O483" t="n">
+        <v>0</v>
+      </c>
+      <c r="P483" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>AES 87513 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>1739166 - 3-122,5 KVA - 89180C0784 - FOR</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>⚠ AE '087513' em múltiplos projetos: 1737374, 1738942, 1739010, 1739166</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr"/>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87513 4600026463 HAGAP.pdf', 'ae': '087513'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>1739225</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J484" t="b">
+        <v>0</v>
+      </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="n">
+        <v>0</v>
+      </c>
+      <c r="O484" t="n">
+        <v>0</v>
+      </c>
+      <c r="P484" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>1739225 -3-112,5KVA - 81776 - V8963 - CFL</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr"/>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1739246</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J485" t="b">
+        <v>0</v>
+      </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="n">
+        <v>0</v>
+      </c>
+      <c r="O485" t="n">
+        <v>0</v>
+      </c>
+      <c r="P485" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>1739246 - 3-112,5KVA - 81776 -V8782 - CFL</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr"/>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>1739340</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J486" t="b">
+        <v>0</v>
+      </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="n">
+        <v>0</v>
+      </c>
+      <c r="O486" t="n">
+        <v>0</v>
+      </c>
+      <c r="P486" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>1739340 - 3-112,5KVA - 81776 V4953 - CBL</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr"/>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>1739341</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J487" t="b">
+        <v>0</v>
+      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="n">
+        <v>0</v>
+      </c>
+      <c r="O487" t="n">
+        <v>0</v>
+      </c>
+      <c r="P487" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>1739341 - 3-112,5KVA - 81776 - V2804 - NAU</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr"/>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>1739344</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J488" t="b">
+        <v>0</v>
+      </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="n">
+        <v>0</v>
+      </c>
+      <c r="O488" t="n">
+        <v>0</v>
+      </c>
+      <c r="P488" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>1739344 - 3-112,5KVA - 81776 - 46871 - CFL</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr"/>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>1739416</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J489" t="b">
+        <v>0</v>
+      </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="n">
+        <v>0</v>
+      </c>
+      <c r="O489" t="n">
+        <v>0</v>
+      </c>
+      <c r="P489" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>1739416 - 3-112,5KVA - 81776 - V8365 - NAU</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr"/>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>1739419</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J490" t="b">
+        <v>0</v>
+      </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="n">
+        <v>0</v>
+      </c>
+      <c r="O490" t="n">
+        <v>0</v>
+      </c>
+      <c r="P490" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>1739419 - 3-112,5KVA - 81776 - V6236 - NAU</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr"/>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>1739431</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J491" t="b">
+        <v>0</v>
+      </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
+      <c r="P491" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>1739431 - 3-112,5KVA - 81776 - V2391 - NAU</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr"/>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>1739436</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>087514</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>DECONSTRUÇÃONADATADE</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>364,932</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>364.932</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>27/11/2026</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>R$27.866,15</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J492" t="b">
+        <v>0</v>
+      </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="n">
+        <v>0</v>
+      </c>
+      <c r="O492" t="n">
+        <v>0</v>
+      </c>
+      <c r="P492" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>AES 87514 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>1739436 - 3-112,5KVA - 81776 - 32248 - CFL</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>⚠ AE '087514' em múltiplos projetos: 1739225, 1739246, 1739340, 1739341, 1739344, 1739416, 1739419, 1739431, 1739436</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr"/>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87514 4600026463 HAGAP.pdf', 'ae': '087514'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>1727315</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>087562</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>555,985</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>555.985</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>R$36.547,97</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J493" t="b">
+        <v>0</v>
+      </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="n">
+        <v>0</v>
+      </c>
+      <c r="O493" t="n">
+        <v>0</v>
+      </c>
+      <c r="P493" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>AES 87562 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>1727315 01.20264266793872 - JOCELIO LUIZ SILOTI 19-10-2026</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>⚠ AE '087562' em múltiplos projetos: 1727315, 1737156, 1738547, 1737788, 1737697</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr"/>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87562 4600026463 HAGAP.pdf', 'ae': '087562'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>1737156</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>087562</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>CARVALHO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>555,985</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>555.985</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>R$36.547,97</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J494" t="b">
+        <v>0</v>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="n">
+        <v>0</v>
+      </c>
+      <c r="O494" t="n">
+        <v>0</v>
+      </c>
+      <c r="P494" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>AES 87562 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>1737156 01.20264955534142 - OSVALDO ARANTES DE OLIVEIRA 26-10-2026</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>⚠ AE '087562' em múltiplos projetos: 1727315, 1737156, 1738547, 1737788, 1737697</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr"/>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87562 4600026463 HAGAP.pdf', 'ae': '087562'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>1738547</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>087562</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>DEDOURADINA DISTVILAFORMOSA</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>555,985</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>555.985</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>R$36.547,97</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J495" t="b">
+        <v>0</v>
+      </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="n">
+        <v>0</v>
+      </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
+      <c r="P495" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>AES 87562 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>1738547 01.20265353737019 - MUNICIPIO DE DOURADINA 26-10-2026</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>⚠ AE '087562' em múltiplos projetos: 1727315, 1737156, 1738547, 1737788, 1737697</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr"/>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87562 4600026463 HAGAP.pdf', 'ae': '087562'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>1737788</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>087562</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>555,985</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>555.985</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>R$36.547,97</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J496" t="b">
+        <v>0</v>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="n">
+        <v>0</v>
+      </c>
+      <c r="O496" t="n">
+        <v>0</v>
+      </c>
+      <c r="P496" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>AES 87562 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>1737788 01.20264954046002 - LEANDRO JUNIOR DA SILVA 19-10-2026</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>⚠ AE '087562' em múltiplos projetos: 1727315, 1737156, 1738547, 1737788, 1737697</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr"/>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87562 4600026463 HAGAP.pdf', 'ae': '087562'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>1737697</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>087562</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>ANUNCIACAO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>555,985</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>555.985</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>R$36.547,97</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J497" t="b">
+        <v>0</v>
+      </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="n">
+        <v>0</v>
+      </c>
+      <c r="O497" t="n">
+        <v>0</v>
+      </c>
+      <c r="P497" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>AES 87562 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>1737697 01.20265013399875 - ELOI CANDIDO DA SILVA MARTINI 16-12-2026</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>⚠ AE '087562' em múltiplos projetos: 1727315, 1737156, 1738547, 1737788, 1737697</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr"/>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87562 4600026463 HAGAP.pdf', 'ae': '087562'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>1738055</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>087563</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>808,092</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>808.092</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>R$53.645,95</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J498" t="b">
+        <v>0</v>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="n">
+        <v>0</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
+      <c r="P498" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>AES 87563 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>1738055 01.20265008240147 - SINVALDO ALVES VIEIRA 09-12-2026</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>⚠ AE '087563' em múltiplos projetos: 1738055, 1737076, 1737774, 1741115</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr"/>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87563 4600026463 HAGAP.pdf', 'ae': '087563'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1737076</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>087563</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>ANUNCIACAO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>808,092</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>808.092</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>R$53.645,95</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J499" t="b">
+        <v>0</v>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
+      <c r="P499" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>AES 87563 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>1737076 01.20264972976818 - SIND DOS EMPREGADOS NA IND DE ALIMENTACAO DE UMUARAMA 09-12-2026</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>⚠ AE '087563' em múltiplos projetos: 1738055, 1737076, 1737774, 1741115</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr"/>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87563 4600026463 HAGAP.pdf', 'ae': '087563'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>1737774</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>087563</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>808,092</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>808.092</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>R$53.645,95</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J500" t="b">
+        <v>0</v>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
+      <c r="N500" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
+      <c r="P500" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>AES 87563 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>1737774 01.20265008381335 - CAMILA DE SOUZA CASTRO 09-12-2026</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>⚠ AE '087563' em múltiplos projetos: 1738055, 1737076, 1737774, 1741115</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr"/>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87563 4600026463 HAGAP.pdf', 'ae': '087563'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>1741115</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>087563</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>LOPES AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>808,092</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>808.092</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>R$53.645,95</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J501" t="b">
+        <v>0</v>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="n">
+        <v>0</v>
+      </c>
+      <c r="O501" t="n">
+        <v>0</v>
+      </c>
+      <c r="P501" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>AES 87563 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>1741115 01.20264151999184 - PARANA TRIBUNAL DE JUSTICA 16-12-2026</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>⚠ AE '087563' em múltiplos projetos: 1738055, 1737076, 1737774, 1741115</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr"/>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87563 4600026463 HAGAP.pdf', 'ae': '087563'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>1732443</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>087564</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>329,972</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>329.972</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>R$25.196,65</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J502" t="b">
+        <v>0</v>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
+      <c r="P502" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>AES 87564 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>1732443 01.20264644363777 - LUIZ SABATINE 23-10-2026</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>⚠ AE '087564' em múltiplos projetos: 1732443, 1735371</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr"/>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87564 4600026463 HAGAP.pdf', 'ae': '087564'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>1735371</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>087564</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>UMUARAMA</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>329,972</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>329.972</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>R$25.196,65</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J503" t="b">
+        <v>0</v>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="n">
+        <v>0</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
+      <c r="P503" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>AES 87564 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>1735371 01.20264851165629 - EPR PARANA S.A 23-12-2026</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>⚠ AE '087564' em múltiplos projetos: 1732443, 1735371</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr"/>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87564 4600026463 HAGAP.pdf', 'ae': '087564'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>1737074</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>ASSISCHATEAUBRIAND</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="n">
+        <v>0</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>30.07.2027</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>R$7,54</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J504" t="b">
+        <v>0</v>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="n">
+        <v>0</v>
+      </c>
+      <c r="O504" t="n">
+        <v>0</v>
+      </c>
+      <c r="P504" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q504" t="inlineStr"/>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>1737074 - LDOT385342026 - BRT - AND - 270US</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr"/>
+      <c r="U504" t="inlineStr"/>
+      <c r="V504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1659017</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="n">
+        <v>0</v>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J505" t="b">
+        <v>0</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
+      <c r="N505" t="n">
+        <v>1</v>
+      </c>
+      <c r="O505" t="n">
+        <v>0</v>
+      </c>
+      <c r="P505" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q505" t="inlineStr"/>
+      <c r="R505" t="inlineStr"/>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>medicao</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr"/>
+      <c r="U505" t="inlineStr"/>
+      <c r="V505" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
